--- a/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
@@ -1391,7 +1391,7 @@
         <v>1.1066</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>5.676</v>
+        <v>10.373216</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>1.1066</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>5.676</v>
+        <v>10.373216</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1493,7 +1493,7 @@
         <v>1.10825</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>5.9433396</v>
+        <v>10.861795</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>1.10825</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>5.9433396</v>
+        <v>10.861795</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>1</v>
@@ -1595,7 +1595,7 @@
         <v>1.1099</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>7.893452996168583</v>
+        <v>14.425739</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
         <v>1.1099</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>7.893452996168583</v>
+        <v>14.425739</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>1</v>
@@ -1697,7 +1697,7 @@
         <v>1.05945</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>5.13074444750958</v>
+        <v>9.37673</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.11155</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>8.957019401785715</v>
+        <v>16.369467</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>1.11155</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>8.957019401785715</v>
+        <v>16.369467</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>1.061025</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>5.822062611160715</v>
+        <v>10.640154</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>1.1132</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>13.95070272174071</v>
+        <v>25.495711</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>1</v>
@@ -1952,7 +1952,7 @@
         <v>1.1132</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>13.95070272174071</v>
+        <v>25.495711</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>1.0626</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>9.067956769131461</v>
+        <v>16.572212</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>1.012</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>21.81889905680247</v>
+        <v>39.875291</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>0.08</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>1</v>
@@ -2105,7 +2105,7 @@
         <v>1.012</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>21.81889905680247</v>
+        <v>39.875291</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>0.08</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="0" t="n">
         <v>1</v>
@@ -2156,7 +2156,7 @@
         <v>1.0135</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>5.93198992443325</v>
+        <v>14.454736</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>1.11485</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>13.18219983207389</v>
+        <v>24.091227</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>1</v>
@@ -2258,7 +2258,7 @@
         <v>1.11485</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>13.18219983207389</v>
+        <v>24.091227</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
@@ -2309,7 +2309,7 @@
         <v>1.6216</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>11.20486985726281</v>
+        <v>20.477543</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>1.0135</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>20.61696053736356</v>
+        <v>37.67868</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>0.08</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>1</v>
@@ -2411,7 +2411,7 @@
         <v>1.064175</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>8.568429890848027</v>
+        <v>15.659298</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>1.6216</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>11.20486985726281</v>
+        <v>20.477543</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>1.0135</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>20.61696053736356</v>
+        <v>37.67868</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>0.08</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
         <v>1.015</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>6.245943526380369</v>
+        <v>15.219761</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>1.1165</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>13.87987450306749</v>
+        <v>25.366268</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="0" t="n">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>1.1165</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>13.87987450306749</v>
+        <v>25.366268</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>1.624</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>11.79789332760736</v>
+        <v>21.561328</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>1.015</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>21.70812372279755</v>
+        <v>39.672843</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>0.08</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>1</v>
@@ -2819,7 +2819,7 @@
         <v>1.06575</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>9.021918426993865</v>
+        <v>16.488074</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1.624</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>11.79789332760736</v>
+        <v>21.561328</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>1.015</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>21.70812372279755</v>
+        <v>39.672843</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>0.08</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="0" t="n">
         <v>1</v>
@@ -2972,7 +2972,7 @@
         <v>1.0165</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>7.412691032512314</v>
+        <v>18.062825</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>1.11815</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>16.47264673891625</v>
+        <v>30.104708</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="0" t="n">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>1.11815</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>16.47264673891625</v>
+        <v>30.104708</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="0" t="n">
         <v>1</v>
@@ -3125,7 +3125,7 @@
         <v>1.6264</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>14.00174972807882</v>
+        <v>25.589002</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.067325</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>10.70722038029557</v>
+        <v>19.56806</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>1.6264</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>14.00174972807882</v>
+        <v>25.589002</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>1.0165</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>25.76321949966502</v>
+        <v>47.083764</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>0.08</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="0" t="n">
         <v>1</v>
@@ -3329,7 +3329,7 @@
         <v>1.0165</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>25.76321949966502</v>
+        <v>47.083764</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0.08</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="0" t="n">
         <v>1</v>
@@ -3380,7 +3380,7 @@
         <v>1.018</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>21.443341</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>1.1198</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>19.55555555555556</v>
+        <v>35.738901</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>1</v>
@@ -3482,7 +3482,7 @@
         <v>1.1198</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>19.55555555555556</v>
+        <v>35.738901</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="0" t="n">
         <v>1</v>
@@ -3533,7 +3533,7 @@
         <v>1.6288</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>16.62222222222222</v>
+        <v>30.378066</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>1.018</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>30.58488888888889</v>
+        <v>55.895641</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>0.08</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="0" t="n">
         <v>1</v>
@@ -3635,7 +3635,7 @@
         <v>1.0689</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>12.71111111111111</v>
+        <v>23.230286</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>1.6288</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>16.62222222222222</v>
+        <v>30.378066</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>1.018</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>30.58488888888889</v>
+        <v>55.895641</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>0.08</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>1.018</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>30.58488888888889</v>
+        <v>55.895641</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>0.08</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>1</v>
@@ -3839,7 +3839,7 @@
         <v>1.0195</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>15.13511868533171</v>
+        <v>36.880398</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>1.12145</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>33.63359707851491</v>
+        <v>61.467331</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>1</v>
@@ -3941,7 +3941,7 @@
         <v>1.12145</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>33.63359707851491</v>
+        <v>61.467331</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>1</v>
@@ -3992,7 +3992,7 @@
         <v>1.6312</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>28.58855751673767</v>
+        <v>52.247231</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>1.0195</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>52.60294583079732</v>
+        <v>96.134905</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>0.08</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>1</v>
@@ -4094,7 +4094,7 @@
         <v>1.070475</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>21.86183810103469</v>
+        <v>39.953765</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>1.6312</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>28.58855751673767</v>
+        <v>52.247231</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>1.0195</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>52.60294583079732</v>
+        <v>96.134905</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>0.08</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>1</v>
@@ -4247,7 +4247,7 @@
         <v>1.0195</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>52.60294583079732</v>
+        <v>96.134905</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>0.08</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>1</v>
@@ -4298,7 +4298,7 @@
         <v>1.1231</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>28.53238866396761</v>
+        <v>52.144579</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" s="0" t="n">
         <v>1</v>
@@ -4349,7 +4349,7 @@
         <v>1.1231</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>28.53238866396761</v>
+        <v>52.144579</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="0" t="n">
         <v>1</v>
@@ -4400,7 +4400,7 @@
         <v>1.6336</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>24.25253036437247</v>
+        <v>44.322892</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>0.8168</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>53.35556680161943</v>
+        <v>97.510363</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>0.15</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>2</v>
@@ -4502,7 +4502,7 @@
         <v>0.8168</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>53.35556680161943</v>
+        <v>97.510363</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>0.15</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>2</v>
@@ -4553,7 +4553,7 @@
         <v>1.021</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>44.62465587044535</v>
+        <v>81.55412200000001</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>0.08</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>1</v>
@@ -4604,7 +4604,7 @@
         <v>1.07205</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>18.54605263157895</v>
+        <v>33.893977</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>1.6336</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>24.25253036437247</v>
+        <v>44.322892</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>1.021</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>44.62465587044535</v>
+        <v>81.55412200000001</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>0.08</v>
       </c>
       <c r="J69" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" s="0" t="n">
         <v>1</v>
@@ -4757,7 +4757,7 @@
         <v>1.021</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>44.62465587044535</v>
+        <v>81.55412200000001</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>0.08</v>
       </c>
       <c r="J70" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" s="0" t="n">
         <v>1</v>
@@ -4808,7 +4808,7 @@
         <v>1.0225</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>12.47008547008547</v>
+        <v>30.386397</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>1.0225</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>12.47008547008547</v>
+        <v>30.386397</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1.12475</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>27.71130104463438</v>
+        <v>50.643995</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" s="0" t="n">
         <v>1</v>
@@ -4961,7 +4961,7 @@
         <v>1.12475</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>27.71130104463438</v>
+        <v>50.643995</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" s="0" t="n">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>1.636</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>23.55460588793922</v>
+        <v>43.047395</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>51.82013295346628</v>
+        <v>94.70426999999999</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>0.15</v>
       </c>
       <c r="J76" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" s="0" t="n">
         <v>2</v>
@@ -5114,7 +5114,7 @@
         <v>1.0225</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>43.34047483380817</v>
+        <v>79.207207</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>0.08</v>
       </c>
       <c r="J77" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77" s="0" t="n">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>1.073625</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>18.01234567901234</v>
+        <v>32.918596</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>51.82013295346628</v>
+        <v>94.70426999999999</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>0.15</v>
       </c>
       <c r="J79" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K79" s="0" t="n">
         <v>2</v>
@@ -5267,7 +5267,7 @@
         <v>1.636</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>23.55460588793922</v>
+        <v>43.047395</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>1.0225</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>43.34047483380817</v>
+        <v>79.207207</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>0.08</v>
       </c>
       <c r="J81" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="0" t="n">
         <v>1</v>
@@ -5369,7 +5369,7 @@
         <v>1.0225</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>43.34047483380817</v>
+        <v>79.207207</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>0.08</v>
       </c>
       <c r="J82" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K82" s="0" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
         <v>1.024</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>14.41944194419442</v>
+        <v>35.136478</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>1.024</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>14.41944194419442</v>
+        <v>35.136478</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>1.1264</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>32.04320432043204</v>
+        <v>58.560797</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K85" s="0" t="n">
         <v>1</v>
@@ -5573,7 +5573,7 @@
         <v>1.1264</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>32.04320432043204</v>
+        <v>58.560797</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" s="0" t="n">
         <v>1</v>
@@ -5624,7 +5624,7 @@
         <v>1.6384</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>27.23672367236723</v>
+        <v>49.776677</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>0.8192</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>59.92079207920792</v>
+        <v>109.50869</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>0.15</v>
       </c>
       <c r="J88" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="0" t="n">
         <v>2</v>
@@ -5726,7 +5726,7 @@
         <v>1.024</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>50.11557155715571</v>
+        <v>91.58908599999999</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>0.08</v>
       </c>
       <c r="J89" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="0" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         <v>1.0752</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>20.82808280828083</v>
+        <v>38.064518</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>0.8192</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>59.92079207920792</v>
+        <v>109.50869</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>0.15</v>
       </c>
       <c r="J91" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K91" s="0" t="n">
         <v>2</v>
@@ -5879,7 +5879,7 @@
         <v>1.6384</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>27.23672367236723</v>
+        <v>49.776677</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>1.024</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>50.11557155715571</v>
+        <v>91.58908599999999</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>0.08</v>
       </c>
       <c r="J93" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" s="0" t="n">
         <v>1</v>
@@ -5981,7 +5981,7 @@
         <v>1.024</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>50.11557155715571</v>
+        <v>91.58908599999999</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>0.08</v>
       </c>
       <c r="J94" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K94" s="0" t="n">
         <v>1</v>
@@ -6032,7 +6032,7 @@
         <v>1.0255</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>16.54491017964072</v>
+        <v>40.315698</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>1.0255</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>16.54491017964072</v>
+        <v>40.315698</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>1.0255</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>16.54491017964072</v>
+        <v>40.315698</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>1.12805</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>36.76646706586826</v>
+        <v>67.192831</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K98" s="0" t="n">
         <v>1</v>
@@ -6236,7 +6236,7 @@
         <v>1.12805</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>36.76646706586826</v>
+        <v>67.192831</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99" s="0" t="n">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>1.6408</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>31.25149700598802</v>
+        <v>57.113906</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>68.75329341317365</v>
+        <v>125.650593</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>0.15</v>
       </c>
       <c r="J101" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K101" s="0" t="n">
         <v>2</v>
@@ -6389,7 +6389,7 @@
         <v>1.0255</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>57.50275449101796</v>
+        <v>105.089587</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>0.08</v>
       </c>
       <c r="J102" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102" s="0" t="n">
         <v>1</v>
@@ -6440,7 +6440,7 @@
         <v>1.076775</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>23.89820359281437</v>
+        <v>43.67534</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>68.75329341317365</v>
+        <v>125.650593</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>0.15</v>
       </c>
       <c r="J104" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K104" s="0" t="n">
         <v>2</v>
@@ -6542,7 +6542,7 @@
         <v>1.6408</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>31.25149700598802</v>
+        <v>57.113906</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>1.0255</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>57.50275449101796</v>
+        <v>105.089587</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>0.08</v>
       </c>
       <c r="J106" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K106" s="0" t="n">
         <v>1</v>
@@ -6644,7 +6644,7 @@
         <v>1.0255</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>57.50275449101796</v>
+        <v>105.089587</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>0.08</v>
       </c>
       <c r="J107" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K107" s="0" t="n">
         <v>1</v>
@@ -6695,7 +6695,7 @@
         <v>1.027</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>26.6728565784275</v>
+        <v>64.99490400000001</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>1.027</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>26.6728565784275</v>
+        <v>64.99490400000001</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>1.027</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>26.6728565784275</v>
+        <v>64.99490400000001</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>1.1297</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>59.27301461872778</v>
+        <v>108.324839</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" s="0" t="n">
         <v>1</v>
@@ -6899,7 +6899,7 @@
         <v>1.1297</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>59.27301461872778</v>
+        <v>108.324839</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K112" s="0" t="n">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>1.6432</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>50.3820624259186</v>
+        <v>92.07611300000001</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>0.7702499999999999</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>221.9181667325168</v>
+        <v>405.568198</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>0.22</v>
       </c>
       <c r="J114" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K114" s="0" t="n">
         <v>2</v>
@@ -7052,7 +7052,7 @@
         <v>0.8216</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>110.8405373370209</v>
+        <v>202.567449</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>0.15</v>
       </c>
       <c r="J115" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K115" s="0" t="n">
         <v>2</v>
@@ -7103,7 +7103,7 @@
         <v>1.027</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>92.70299486369024</v>
+        <v>169.420049</v>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>0.08</v>
       </c>
       <c r="J116" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K116" s="0" t="n">
         <v>1</v>
@@ -7154,7 +7154,7 @@
         <v>1.07835</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>38.52745950217306</v>
+        <v>70.411145</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>0.8216</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>110.8405373370209</v>
+        <v>202.567449</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>0.15</v>
       </c>
       <c r="J118" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K118" s="0" t="n">
         <v>2</v>
@@ -7256,7 +7256,7 @@
         <v>1.6432</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>50.3820624259186</v>
+        <v>92.07611300000001</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>1.027</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>92.70299486369024</v>
+        <v>169.420049</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>0.08</v>
       </c>
       <c r="J120" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K120" s="0" t="n">
         <v>1</v>
@@ -7358,7 +7358,7 @@
         <v>1.027</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>92.70299486369024</v>
+        <v>169.420049</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>0.08</v>
       </c>
       <c r="J121" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K121" s="0" t="n">
         <v>1</v>
@@ -7409,7 +7409,7 @@
         <v>1.13135</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>59.20309477756286</v>
+        <v>108.197057</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K122" s="0" t="n">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         <v>1.13135</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>59.20309477756286</v>
+        <v>108.197057</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K123" s="0" t="n">
         <v>1</v>
@@ -7511,7 +7511,7 @@
         <v>1.6456</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>50.32263056092843</v>
+        <v>91.96749800000001</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>0.8228</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>110.7097872340426</v>
+        <v>202.328496</v>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>0.15</v>
       </c>
       <c r="J125" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K125" s="0" t="n">
         <v>2</v>
@@ -7613,7 +7613,7 @@
         <v>1.0285</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>92.59364023210831</v>
+        <v>169.220197</v>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>0.08</v>
       </c>
       <c r="J126" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K126" s="0" t="n">
         <v>1</v>
@@ -7664,7 +7664,7 @@
         <v>1.079925</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>38.48201160541586</v>
+        <v>70.328087</v>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>0.8228</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>110.7097872340426</v>
+        <v>202.328496</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>0.15</v>
       </c>
       <c r="J128" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K128" s="0" t="n">
         <v>2</v>
@@ -7766,7 +7766,7 @@
         <v>1.6456</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>50.32263056092843</v>
+        <v>91.96749800000001</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>1.0285</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>92.59364023210831</v>
+        <v>169.220197</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>0.08</v>
       </c>
       <c r="J130" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K130" s="0" t="n">
         <v>1</v>
@@ -7868,7 +7868,7 @@
         <v>1.0285</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>92.59364023210831</v>
+        <v>169.220197</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>0.08</v>
       </c>
       <c r="J131" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K131" s="0" t="n">
         <v>1</v>
@@ -7919,7 +7919,7 @@
         <v>1.03</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>25.78128440366972</v>
+        <v>62.822371</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>1.03</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>25.78128440366972</v>
+        <v>62.822371</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>1.03</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>25.78128440366972</v>
+        <v>62.822371</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>1.133</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>57.29174311926604</v>
+        <v>104.703952</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" s="0" t="n">
         <v>1</v>
@@ -8123,7 +8123,7 @@
         <v>1.133</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>57.29174311926604</v>
+        <v>104.703952</v>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K136" s="0" t="n">
         <v>1</v>
@@ -8174,7 +8174,7 @@
         <v>1.648</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>48.69798165137613</v>
+        <v>88.99835899999999</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>107.1355596330275</v>
+        <v>195.79639</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>0.15</v>
       </c>
       <c r="J138" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K138" s="0" t="n">
         <v>2</v>
@@ -8276,7 +8276,7 @@
         <v>1.03</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>89.60428623853208</v>
+        <v>163.75698</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0.08</v>
       </c>
       <c r="J139" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K139" s="0" t="n">
         <v>1</v>
@@ -8327,7 +8327,7 @@
         <v>1.0815</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>37.23963302752293</v>
+        <v>68.057569</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>107.1355596330275</v>
+        <v>195.79639</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>0.15</v>
       </c>
       <c r="J141" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K141" s="0" t="n">
         <v>2</v>
@@ -8429,7 +8429,7 @@
         <v>1.648</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>48.69798165137613</v>
+        <v>88.99835899999999</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>1.03</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>89.60428623853208</v>
+        <v>163.75698</v>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>0.08</v>
       </c>
       <c r="J143" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K143" s="0" t="n">
         <v>1</v>
@@ -8531,7 +8531,7 @@
         <v>1.03</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>89.60428623853208</v>
+        <v>163.75698</v>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>0.08</v>
       </c>
       <c r="J144" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K144" s="0" t="n">
         <v>1</v>
@@ -8582,7 +8582,7 @@
         <v>1.0315</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>26.41731175228712</v>
+        <v>64.37220600000001</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>1.0315</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>26.41731175228712</v>
+        <v>64.37220600000001</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>1.0315</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>26.41731175228712</v>
+        <v>64.37220600000001</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>1.13465</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>58.70513722730472</v>
+        <v>107.287011</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K148" s="0" t="n">
         <v>1</v>
@@ -8786,7 +8786,7 @@
         <v>1.13465</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>58.70513722730472</v>
+        <v>107.287011</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K149" s="0" t="n">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         <v>1.6504</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>49.89936664320901</v>
+        <v>91.19395900000001</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>109.7786066150598</v>
+        <v>200.62671</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>0.15</v>
       </c>
       <c r="J151" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K151" s="0" t="n">
         <v>2</v>
@@ -8939,7 +8939,7 @@
         <v>1.0315</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>91.81483462350458</v>
+        <v>167.796885</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>0.08</v>
       </c>
       <c r="J152" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K152" s="0" t="n">
         <v>1</v>
@@ -8990,7 +8990,7 @@
         <v>1.083075</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>38.15833919774807</v>
+        <v>69.736557</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>109.7786066150598</v>
+        <v>200.62671</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>0.15</v>
       </c>
       <c r="J154" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K154" s="0" t="n">
         <v>2</v>
@@ -9092,7 +9092,7 @@
         <v>1.6504</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>49.89936664320901</v>
+        <v>91.19395900000001</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>1.0315</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>91.81483462350458</v>
+        <v>167.796885</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>0.08</v>
       </c>
       <c r="J156" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K156" s="0" t="n">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>1.0315</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>91.81483462350458</v>
+        <v>167.796885</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>0.08</v>
       </c>
       <c r="J157" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K157" s="0" t="n">
         <v>1</v>
@@ -9245,7 +9245,7 @@
         <v>1.033</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>29.25302826379543</v>
+        <v>71.28211899999999</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>1.033</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>29.25302826379543</v>
+        <v>71.28211899999999</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.033</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>29.25302826379543</v>
+        <v>71.28211899999999</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>1.1363</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>65.00672947510094</v>
+        <v>118.803532</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K161" s="0" t="n">
         <v>1</v>
@@ -9449,7 +9449,7 @@
         <v>1.1363</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>65.00672947510094</v>
+        <v>118.803532</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K162" s="0" t="n">
         <v>1</v>
@@ -9500,7 +9500,7 @@
         <v>1.6528</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>55.2557200538358</v>
+        <v>100.983003</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>0.8264</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>121.5625841184388</v>
+        <v>222.162606</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>0.15</v>
       </c>
       <c r="J164" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K164" s="0" t="n">
         <v>2</v>
@@ -9602,7 +9602,7 @@
         <v>1.033</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>101.6705248990579</v>
+        <v>185.808725</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>0.08</v>
       </c>
       <c r="J165" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K165" s="0" t="n">
         <v>1</v>
@@ -9653,7 +9653,7 @@
         <v>1.08465</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>42.25437415881562</v>
+        <v>77.222296</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>0.8264</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>121.5625841184388</v>
+        <v>222.162606</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>0.15</v>
       </c>
       <c r="J167" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K167" s="0" t="n">
         <v>2</v>
@@ -9755,7 +9755,7 @@
         <v>0.8264</v>
       </c>
       <c r="D168" s="0" t="n">
-        <v>121.5625841184388</v>
+        <v>222.162606</v>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>0.15</v>
       </c>
       <c r="J168" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K168" s="0" t="n">
         <v>2</v>
@@ -9806,7 +9806,7 @@
         <v>1.6528</v>
       </c>
       <c r="D169" s="0" t="n">
-        <v>55.2557200538358</v>
+        <v>100.983003</v>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>1.033</v>
       </c>
       <c r="D170" s="0" t="n">
-        <v>101.6705248990579</v>
+        <v>185.808725</v>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>0.08</v>
       </c>
       <c r="J170" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K170" s="0" t="n">
         <v>1</v>
@@ -9908,7 +9908,7 @@
         <v>1.033</v>
       </c>
       <c r="D171" s="0" t="n">
-        <v>101.6705248990579</v>
+        <v>185.808725</v>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>0.08</v>
       </c>
       <c r="J171" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K171" s="0" t="n">
         <v>1</v>
@@ -9959,7 +9959,7 @@
         <v>1.0345</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>46.15486725663717</v>
+        <v>112.467562</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>1.0345</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>46.15486725663717</v>
+        <v>112.467562</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>1.0345</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>46.15486725663717</v>
+        <v>112.467562</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>1.13795</v>
       </c>
       <c r="D175" s="0" t="n">
-        <v>102.5663716814159</v>
+        <v>187.445936</v>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K175" s="0" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
         <v>1.13795</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>102.5663716814159</v>
+        <v>187.445936</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176" s="0" t="n">
         <v>1</v>
@@ -10214,7 +10214,7 @@
         <v>1.6552</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>87.18141592920355</v>
+        <v>159.329046</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>0.8276</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>191.7991150442478</v>
+        <v>350.523901</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>0.15</v>
       </c>
       <c r="J178" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K178" s="0" t="n">
         <v>2</v>
@@ -10316,7 +10316,7 @@
         <v>0.8276</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>191.7991150442478</v>
+        <v>350.523901</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>0.15</v>
       </c>
       <c r="J179" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K179" s="0" t="n">
         <v>2</v>
@@ -10367,7 +10367,7 @@
         <v>1.0345</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>160.4138053097346</v>
+        <v>293.165444</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>0.08</v>
       </c>
       <c r="J180" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K180" s="0" t="n">
         <v>1</v>
@@ -10418,7 +10418,7 @@
         <v>1.086225</v>
       </c>
       <c r="D181" s="0" t="n">
-        <v>66.66814159292035</v>
+        <v>121.839859</v>
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>0.8276</v>
       </c>
       <c r="D182" s="0" t="n">
-        <v>191.7991150442478</v>
+        <v>350.523901</v>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>0.15</v>
       </c>
       <c r="J182" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K182" s="0" t="n">
         <v>2</v>
@@ -10520,7 +10520,7 @@
         <v>1.6552</v>
       </c>
       <c r="D183" s="0" t="n">
-        <v>87.18141592920355</v>
+        <v>159.329046</v>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.0345</v>
       </c>
       <c r="D184" s="0" t="n">
-        <v>160.4138053097346</v>
+        <v>293.165444</v>
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>0.08</v>
       </c>
       <c r="J184" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K184" s="0" t="n">
         <v>1</v>
@@ -10622,7 +10622,7 @@
         <v>1.0345</v>
       </c>
       <c r="D185" s="0" t="n">
-        <v>160.4138053097346</v>
+        <v>293.165444</v>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>0.08</v>
       </c>
       <c r="J185" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K185" s="0" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         <v>1.012</v>
       </c>
       <c r="D186" s="0" t="n">
-        <v>21.81889905680247</v>
+        <v>39.875291</v>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>0.08</v>
       </c>
       <c r="J186" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K186" s="0" t="n">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>1.0135</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>5.93198992443325</v>
+        <v>14.454736</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>1.0135</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>20.61696053736356</v>
+        <v>37.67868</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>0.08</v>
       </c>
       <c r="J188" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K188" s="0" t="n">
         <v>1</v>
@@ -10826,7 +10826,7 @@
         <v>1.015</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>6.245943526380369</v>
+        <v>15.219761</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>1.015</v>
       </c>
       <c r="D190" s="0" t="n">
-        <v>21.70812372279755</v>
+        <v>39.672843</v>
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>0.08</v>
       </c>
       <c r="J190" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K190" s="0" t="n">
         <v>1</v>
@@ -10928,7 +10928,7 @@
         <v>1.0165</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>7.412691032512314</v>
+        <v>18.062825</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>1.0165</v>
       </c>
       <c r="D192" s="0" t="n">
-        <v>25.76321949966502</v>
+        <v>47.083764</v>
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>0.08</v>
       </c>
       <c r="J192" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K192" s="0" t="n">
         <v>1</v>
@@ -11030,7 +11030,7 @@
         <v>1.018</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>21.443341</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>1.018</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>21.443341</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>1.0195</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>15.13511868533171</v>
+        <v>36.880398</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>1.0195</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>15.13511868533171</v>
+        <v>36.880398</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>0.8168</v>
       </c>
       <c r="D197" s="0" t="n">
-        <v>53.35556680161943</v>
+        <v>97.510363</v>
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>0.15</v>
       </c>
       <c r="J197" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K197" s="0" t="n">
         <v>2</v>
@@ -11285,7 +11285,7 @@
         <v>0.8168</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>53.35556680161943</v>
+        <v>97.510363</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>0.15</v>
       </c>
       <c r="J198" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K198" s="0" t="n">
         <v>2</v>
@@ -11336,7 +11336,7 @@
         <v>1.0225</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>12.47008547008547</v>
+        <v>30.386397</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>51.82013295346628</v>
+        <v>94.70426999999999</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>0.15</v>
       </c>
       <c r="J200" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K200" s="0" t="n">
         <v>2</v>
@@ -11438,7 +11438,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D201" s="0" t="n">
-        <v>51.82013295346628</v>
+        <v>94.70426999999999</v>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>0.15</v>
       </c>
       <c r="J201" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K201" s="0" t="n">
         <v>2</v>
@@ -11489,7 +11489,7 @@
         <v>1.024</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>14.41944194419442</v>
+        <v>35.136478</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>0.8192</v>
       </c>
       <c r="D203" s="0" t="n">
-        <v>59.92079207920792</v>
+        <v>109.50869</v>
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>0.15</v>
       </c>
       <c r="J203" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K203" s="0" t="n">
         <v>2</v>
@@ -11591,7 +11591,7 @@
         <v>0.8192</v>
       </c>
       <c r="D204" s="0" t="n">
-        <v>59.92079207920792</v>
+        <v>109.50869</v>
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>0.15</v>
       </c>
       <c r="J204" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K204" s="0" t="n">
         <v>2</v>
@@ -11642,7 +11642,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D205" s="0" t="n">
-        <v>68.75329341317365</v>
+        <v>125.650593</v>
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>0.15</v>
       </c>
       <c r="J205" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K205" s="0" t="n">
         <v>2</v>
@@ -11693,7 +11693,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D206" s="0" t="n">
-        <v>68.75329341317365</v>
+        <v>125.650593</v>
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>0.15</v>
       </c>
       <c r="J206" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K206" s="0" t="n">
         <v>2</v>
@@ -11744,7 +11744,7 @@
         <v>0.8216</v>
       </c>
       <c r="D207" s="0" t="n">
-        <v>110.8405373370209</v>
+        <v>202.567449</v>
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>0.15</v>
       </c>
       <c r="J207" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K207" s="0" t="n">
         <v>2</v>
@@ -11795,7 +11795,7 @@
         <v>0.8216</v>
       </c>
       <c r="D208" s="0" t="n">
-        <v>110.8405373370209</v>
+        <v>202.567449</v>
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>0.15</v>
       </c>
       <c r="J208" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K208" s="0" t="n">
         <v>2</v>
@@ -11846,7 +11846,7 @@
         <v>0.8228</v>
       </c>
       <c r="D209" s="0" t="n">
-        <v>110.7097872340426</v>
+        <v>202.328496</v>
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>0.15</v>
       </c>
       <c r="J209" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K209" s="0" t="n">
         <v>2</v>
@@ -11897,7 +11897,7 @@
         <v>0.8228</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>110.7097872340426</v>
+        <v>202.328496</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>0.15</v>
       </c>
       <c r="J210" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K210" s="0" t="n">
         <v>2</v>
@@ -11948,7 +11948,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>107.1355596330275</v>
+        <v>195.79639</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>0.15</v>
       </c>
       <c r="J211" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K211" s="0" t="n">
         <v>2</v>
@@ -11999,7 +11999,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>107.1355596330275</v>
+        <v>195.79639</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>0.15</v>
       </c>
       <c r="J212" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K212" s="0" t="n">
         <v>2</v>
@@ -12050,7 +12050,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>109.7786066150598</v>
+        <v>200.62671</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>0.15</v>
       </c>
       <c r="J213" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K213" s="0" t="n">
         <v>2</v>
@@ -12101,7 +12101,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>109.7786066150598</v>
+        <v>200.62671</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>0.15</v>
       </c>
       <c r="J214" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K214" s="0" t="n">
         <v>2</v>
@@ -12152,7 +12152,7 @@
         <v>0.8264</v>
       </c>
       <c r="D215" s="0" t="n">
-        <v>121.5625841184388</v>
+        <v>222.162606</v>
       </c>
       <c r="E215" s="0" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>0.15</v>
       </c>
       <c r="J215" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K215" s="0" t="n">
         <v>2</v>
@@ -12203,7 +12203,7 @@
         <v>0.775875</v>
       </c>
       <c r="D216" s="0" t="n">
-        <v>384.0084955752213</v>
+        <v>701.797585</v>
       </c>
       <c r="E216" s="0" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>0.22</v>
       </c>
       <c r="J216" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K216" s="0" t="n">
         <v>2</v>
@@ -12254,7 +12254,7 @@
         <v>0.8276</v>
       </c>
       <c r="D217" s="0" t="n">
-        <v>191.7991150442478</v>
+        <v>350.523901</v>
       </c>
       <c r="E217" s="0" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>0.15</v>
       </c>
       <c r="J217" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K217" s="0" t="n">
         <v>2</v>
@@ -12305,7 +12305,7 @@
         <v>1.036</v>
       </c>
       <c r="D218" s="0" t="n">
-        <v>46.28931013051584</v>
+        <v>112.795165</v>
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>1.036</v>
       </c>
       <c r="D219" s="0" t="n">
-        <v>46.28931013051584</v>
+        <v>112.795165</v>
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>1.036</v>
       </c>
       <c r="D220" s="0" t="n">
-        <v>46.28931013051584</v>
+        <v>112.795165</v>
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>1.1396</v>
       </c>
       <c r="D221" s="0" t="n">
-        <v>102.8651336233685</v>
+        <v>187.991941</v>
       </c>
       <c r="E221" s="0" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="J221" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K221" s="0" t="n">
         <v>1</v>
@@ -12509,7 +12509,7 @@
         <v>1.1396</v>
       </c>
       <c r="D222" s="0" t="n">
-        <v>102.8651336233685</v>
+        <v>187.991941</v>
       </c>
       <c r="E222" s="0" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="J222" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K222" s="0" t="n">
         <v>1</v>
@@ -12560,7 +12560,7 @@
         <v>1.6576</v>
       </c>
       <c r="D223" s="0" t="n">
-        <v>87.43536357986326</v>
+        <v>159.79315</v>
       </c>
       <c r="E223" s="0" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D224" s="0" t="n">
-        <v>192.3577998756992</v>
+        <v>351.544929</v>
       </c>
       <c r="E224" s="0" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>0.15</v>
       </c>
       <c r="J224" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K224" s="0" t="n">
         <v>2</v>
@@ -12662,7 +12662,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D225" s="0" t="n">
-        <v>192.3577998756992</v>
+        <v>351.544929</v>
       </c>
       <c r="E225" s="0" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>0.15</v>
       </c>
       <c r="J225" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K225" s="0" t="n">
         <v>2</v>
@@ -12713,7 +12713,7 @@
         <v>1.036</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>160.8810689869484</v>
+        <v>294.019396</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>0.08</v>
       </c>
       <c r="J226" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K226" s="0" t="n">
         <v>1</v>
@@ -12764,7 +12764,7 @@
         <v>1.0878</v>
       </c>
       <c r="D227" s="0" t="n">
-        <v>66.86233685518955</v>
+        <v>122.194762</v>
       </c>
       <c r="E227" s="0" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D228" s="0" t="n">
-        <v>192.3577998756992</v>
+        <v>351.544929</v>
       </c>
       <c r="E228" s="0" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>0.15</v>
       </c>
       <c r="J228" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228" s="0" t="n">
         <v>2</v>
@@ -12866,7 +12866,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D229" s="0" t="n">
-        <v>192.3577998756992</v>
+        <v>351.544929</v>
       </c>
       <c r="E229" s="0" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>0.15</v>
       </c>
       <c r="J229" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K229" s="0" t="n">
         <v>2</v>
@@ -12917,7 +12917,7 @@
         <v>1.6576</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>87.43536357986326</v>
+        <v>159.79315</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>1.036</v>
       </c>
       <c r="D231" s="0" t="n">
-        <v>160.8810689869484</v>
+        <v>294.019396</v>
       </c>
       <c r="E231" s="0" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>0.08</v>
       </c>
       <c r="J231" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K231" s="0" t="n">
         <v>1</v>
@@ -13019,7 +13019,7 @@
         <v>1.036</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>160.8810689869484</v>
+        <v>294.019396</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>0.08</v>
       </c>
       <c r="J232" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K232" s="0" t="n">
         <v>1</v>
@@ -13070,7 +13070,7 @@
         <v>1.0375</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>45.23578445966062</v>
+        <v>110.227993</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>1.0375</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>45.23578445966062</v>
+        <v>110.227993</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>1.0375</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>45.23578445966062</v>
+        <v>110.227993</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>1.14125</v>
       </c>
       <c r="D236" s="0" t="n">
-        <v>100.5239654659125</v>
+        <v>183.713322</v>
       </c>
       <c r="E236" s="0" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K236" s="0" t="n">
         <v>1</v>
@@ -13274,7 +13274,7 @@
         <v>1.14125</v>
       </c>
       <c r="D237" s="0" t="n">
-        <v>100.5239654659125</v>
+        <v>183.713322</v>
       </c>
       <c r="E237" s="0" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K237" s="0" t="n">
         <v>1</v>
@@ -13325,7 +13325,7 @@
         <v>1.66</v>
       </c>
       <c r="D238" s="0" t="n">
-        <v>85.44537064602561</v>
+        <v>156.156323</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D239" s="0" t="n">
-        <v>187.9798154212564</v>
+        <v>343.543911</v>
       </c>
       <c r="E239" s="0" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>0.15</v>
       </c>
       <c r="J239" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K239" s="0" t="n">
         <v>2</v>
@@ -13427,7 +13427,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D240" s="0" t="n">
-        <v>187.9798154212564</v>
+        <v>343.543911</v>
       </c>
       <c r="E240" s="0" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>0.15</v>
       </c>
       <c r="J240" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K240" s="0" t="n">
         <v>2</v>
@@ -13478,7 +13478,7 @@
         <v>1.0375</v>
       </c>
       <c r="D241" s="0" t="n">
-        <v>157.2194819886871</v>
+        <v>287.327635</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>0.08</v>
       </c>
       <c r="J241" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K241" s="0" t="n">
         <v>1</v>
@@ -13529,7 +13529,7 @@
         <v>1.089375</v>
       </c>
       <c r="D242" s="0" t="n">
-        <v>65.34057755284311</v>
+        <v>119.413659</v>
       </c>
       <c r="E242" s="0" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D243" s="0" t="n">
-        <v>187.9798154212564</v>
+        <v>343.543911</v>
       </c>
       <c r="E243" s="0" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>0.15</v>
       </c>
       <c r="J243" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K243" s="0" t="n">
         <v>2</v>
@@ -13631,7 +13631,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D244" s="0" t="n">
-        <v>187.9798154212564</v>
+        <v>343.543911</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>0.15</v>
       </c>
       <c r="J244" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K244" s="0" t="n">
         <v>2</v>
@@ -13682,7 +13682,7 @@
         <v>1.66</v>
       </c>
       <c r="D245" s="0" t="n">
-        <v>85.44537064602561</v>
+        <v>156.156323</v>
       </c>
       <c r="E245" s="0" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>1.0375</v>
       </c>
       <c r="D246" s="0" t="n">
-        <v>157.2194819886871</v>
+        <v>287.327635</v>
       </c>
       <c r="E246" s="0" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>0.08</v>
       </c>
       <c r="J246" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K246" s="0" t="n">
         <v>1</v>
@@ -13784,7 +13784,7 @@
         <v>1.0375</v>
       </c>
       <c r="D247" s="0" t="n">
-        <v>157.2194819886871</v>
+        <v>287.327635</v>
       </c>
       <c r="E247" s="0" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>0.08</v>
       </c>
       <c r="J247" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K247" s="0" t="n">
         <v>1</v>
@@ -13835,7 +13835,7 @@
         <v>1.039</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>44.63968894009216</v>
+        <v>108.775461</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>1.039</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>44.63968894009216</v>
+        <v>108.775461</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>1.039</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>44.63968894009216</v>
+        <v>108.775461</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>1.1429</v>
       </c>
       <c r="D251" s="0" t="n">
-        <v>99.19930875576037</v>
+        <v>181.292435</v>
       </c>
       <c r="E251" s="0" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K251" s="0" t="n">
         <v>1</v>
@@ -14039,7 +14039,7 @@
         <v>1.1429</v>
       </c>
       <c r="D252" s="0" t="n">
-        <v>99.19930875576037</v>
+        <v>181.292435</v>
       </c>
       <c r="E252" s="0" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K252" s="0" t="n">
         <v>1</v>
@@ -14090,7 +14090,7 @@
         <v>1.6624</v>
       </c>
       <c r="D253" s="0" t="n">
-        <v>84.31941244239631</v>
+        <v>154.09857</v>
       </c>
       <c r="E253" s="0" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D254" s="0" t="n">
-        <v>185.5027073732719</v>
+        <v>339.016854</v>
       </c>
       <c r="E254" s="0" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>0.15</v>
       </c>
       <c r="J254" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K254" s="0" t="n">
         <v>2</v>
@@ -14192,7 +14192,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D255" s="0" t="n">
-        <v>185.5027073732719</v>
+        <v>339.016854</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>0.15</v>
       </c>
       <c r="J255" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K255" s="0" t="n">
         <v>2</v>
@@ -14243,7 +14243,7 @@
         <v>1.039</v>
       </c>
       <c r="D256" s="0" t="n">
-        <v>155.1477188940092</v>
+        <v>283.541369</v>
       </c>
       <c r="E256" s="0" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>0.08</v>
       </c>
       <c r="J256" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K256" s="0" t="n">
         <v>1</v>
@@ -14294,7 +14294,7 @@
         <v>1.09095</v>
       </c>
       <c r="D257" s="0" t="n">
-        <v>64.47955069124424</v>
+        <v>117.840083</v>
       </c>
       <c r="E257" s="0" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D258" s="0" t="n">
-        <v>185.5027073732719</v>
+        <v>339.016854</v>
       </c>
       <c r="E258" s="0" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>0.15</v>
       </c>
       <c r="J258" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K258" s="0" t="n">
         <v>2</v>
@@ -14396,7 +14396,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D259" s="0" t="n">
-        <v>185.5027073732719</v>
+        <v>339.016854</v>
       </c>
       <c r="E259" s="0" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>0.15</v>
       </c>
       <c r="J259" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K259" s="0" t="n">
         <v>2</v>
@@ -14447,7 +14447,7 @@
         <v>1.6624</v>
       </c>
       <c r="D260" s="0" t="n">
-        <v>84.31941244239631</v>
+        <v>154.09857</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>1.039</v>
       </c>
       <c r="D261" s="0" t="n">
-        <v>155.1477188940092</v>
+        <v>283.541369</v>
       </c>
       <c r="E261" s="0" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>0.08</v>
       </c>
       <c r="J261" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K261" s="0" t="n">
         <v>1</v>
@@ -14549,7 +14549,7 @@
         <v>1.039</v>
       </c>
       <c r="D262" s="0" t="n">
-        <v>155.1477188940092</v>
+        <v>283.541369</v>
       </c>
       <c r="E262" s="0" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>0.08</v>
       </c>
       <c r="J262" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K262" s="0" t="n">
         <v>1</v>
@@ -14600,7 +14600,7 @@
         <v>1.0405</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>46.21553884711779</v>
+        <v>112.615403</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>1.0405</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>46.21553884711779</v>
+        <v>112.615403</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>1.0405</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>46.21553884711779</v>
+        <v>112.615403</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>1.14455</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>102.7011974380395</v>
+        <v>187.692338</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K266" s="0" t="n">
         <v>1</v>
@@ -14804,7 +14804,7 @@
         <v>1.14455</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>102.7011974380395</v>
+        <v>187.692338</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K267" s="0" t="n">
         <v>1</v>
@@ -14855,7 +14855,7 @@
         <v>1.6648</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>87.29601782233361</v>
+        <v>159.538487</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>0.8324</v>
       </c>
       <c r="D269" s="0" t="n">
-        <v>192.0512392091339</v>
+        <v>350.984672</v>
       </c>
       <c r="E269" s="0" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>0.15</v>
       </c>
       <c r="J269" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K269" s="0" t="n">
         <v>2</v>
@@ -14957,7 +14957,7 @@
         <v>0.8324</v>
       </c>
       <c r="D270" s="0" t="n">
-        <v>192.0512392091339</v>
+        <v>350.984672</v>
       </c>
       <c r="E270" s="0" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>0.15</v>
       </c>
       <c r="J270" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K270" s="0" t="n">
         <v>2</v>
@@ -15008,7 +15008,7 @@
         <v>1.0405</v>
       </c>
       <c r="D271" s="0" t="n">
-        <v>160.6246727930939</v>
+        <v>293.550817</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>0.08</v>
       </c>
       <c r="J271" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K271" s="0" t="n">
         <v>1</v>
@@ -15059,7 +15059,7 @@
         <v>1.092525</v>
       </c>
       <c r="D272" s="0" t="n">
-        <v>66.7557783347257</v>
+        <v>122.00002</v>
       </c>
       <c r="E272" s="0" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>0.8324</v>
       </c>
       <c r="D273" s="0" t="n">
-        <v>192.0512392091339</v>
+        <v>350.984672</v>
       </c>
       <c r="E273" s="0" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>0.15</v>
       </c>
       <c r="J273" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K273" s="0" t="n">
         <v>2</v>
@@ -15161,7 +15161,7 @@
         <v>0.8324</v>
       </c>
       <c r="D274" s="0" t="n">
-        <v>192.0512392091339</v>
+        <v>350.984672</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>0.15</v>
       </c>
       <c r="J274" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K274" s="0" t="n">
         <v>2</v>
@@ -15212,7 +15212,7 @@
         <v>1.6648</v>
       </c>
       <c r="D275" s="0" t="n">
-        <v>87.29601782233361</v>
+        <v>159.538487</v>
       </c>
       <c r="E275" s="0" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>1.0405</v>
       </c>
       <c r="D276" s="0" t="n">
-        <v>160.6246727930939</v>
+        <v>293.550817</v>
       </c>
       <c r="E276" s="0" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>0.08</v>
       </c>
       <c r="J276" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K276" s="0" t="n">
         <v>1</v>
@@ -15314,7 +15314,7 @@
         <v>1.0405</v>
       </c>
       <c r="D277" s="0" t="n">
-        <v>160.6246727930939</v>
+        <v>293.550817</v>
       </c>
       <c r="E277" s="0" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>0.08</v>
       </c>
       <c r="J277" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K277" s="0" t="n">
         <v>1</v>
@@ -15365,7 +15365,7 @@
         <v>1.042</v>
       </c>
       <c r="D278" s="0" t="n">
-        <v>87.55496828752644</v>
+        <v>213.348979</v>
       </c>
       <c r="E278" s="0" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>1.042</v>
       </c>
       <c r="D279" s="0" t="n">
-        <v>87.55496828752644</v>
+        <v>213.348979</v>
       </c>
       <c r="E279" s="0" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>1.042</v>
       </c>
       <c r="D280" s="0" t="n">
-        <v>87.55496828752644</v>
+        <v>213.348979</v>
       </c>
       <c r="E280" s="0" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>1.1462</v>
       </c>
       <c r="D281" s="0" t="n">
-        <v>194.5665961945032</v>
+        <v>355.581632</v>
       </c>
       <c r="E281" s="0" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="J281" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K281" s="0" t="n">
         <v>1</v>
@@ -15569,7 +15569,7 @@
         <v>1.1462</v>
       </c>
       <c r="D282" s="0" t="n">
-        <v>194.5665961945032</v>
+        <v>355.581632</v>
       </c>
       <c r="E282" s="0" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>0</v>
       </c>
       <c r="J282" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K282" s="0" t="n">
         <v>1</v>
@@ -15620,7 +15620,7 @@
         <v>1.6672</v>
       </c>
       <c r="D283" s="0" t="n">
-        <v>165.3816067653277</v>
+        <v>302.244387</v>
       </c>
       <c r="E283" s="0" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D284" s="0" t="n">
-        <v>363.8395348837209</v>
+        <v>664.937651</v>
       </c>
       <c r="E284" s="0" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>0.15</v>
       </c>
       <c r="J284" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K284" s="0" t="n">
         <v>2</v>
@@ -15722,7 +15722,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D285" s="0" t="n">
-        <v>363.8395348837209</v>
+        <v>664.937651</v>
       </c>
       <c r="E285" s="0" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>0.15</v>
       </c>
       <c r="J285" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K285" s="0" t="n">
         <v>2</v>
@@ -15773,7 +15773,7 @@
         <v>1.042</v>
       </c>
       <c r="D286" s="0" t="n">
-        <v>304.302156448203</v>
+        <v>556.129672</v>
       </c>
       <c r="E286" s="0" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>0.08</v>
       </c>
       <c r="J286" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K286" s="0" t="n">
         <v>1</v>
@@ -15824,7 +15824,7 @@
         <v>1.0941</v>
       </c>
       <c r="D287" s="0" t="n">
-        <v>126.4682875264271</v>
+        <v>231.128061</v>
       </c>
       <c r="E287" s="0" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D288" s="0" t="n">
-        <v>363.8395348837209</v>
+        <v>664.937651</v>
       </c>
       <c r="E288" s="0" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>0.15</v>
       </c>
       <c r="J288" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K288" s="0" t="n">
         <v>2</v>
@@ -15926,7 +15926,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D289" s="0" t="n">
-        <v>363.8395348837209</v>
+        <v>664.937651</v>
       </c>
       <c r="E289" s="0" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>0.15</v>
       </c>
       <c r="J289" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K289" s="0" t="n">
         <v>2</v>
@@ -15977,7 +15977,7 @@
         <v>1.6672</v>
       </c>
       <c r="D290" s="0" t="n">
-        <v>165.3816067653277</v>
+        <v>302.244387</v>
       </c>
       <c r="E290" s="0" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>1.042</v>
       </c>
       <c r="D291" s="0" t="n">
-        <v>304.302156448203</v>
+        <v>556.129672</v>
       </c>
       <c r="E291" s="0" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>0.08</v>
       </c>
       <c r="J291" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K291" s="0" t="n">
         <v>1</v>
@@ -16079,7 +16079,7 @@
         <v>0.7815000000000001</v>
       </c>
       <c r="D292" s="0" t="n">
-        <v>728.4573361522199</v>
+        <v>1331.297629</v>
       </c>
       <c r="E292" s="0" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>0.22</v>
       </c>
       <c r="J292" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K292" s="0" t="n">
         <v>2</v>
@@ -16130,7 +16130,7 @@
         <v>1.042</v>
       </c>
       <c r="D293" s="0" t="n">
-        <v>304.302156448203</v>
+        <v>556.129672</v>
       </c>
       <c r="E293" s="0" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>0.08</v>
       </c>
       <c r="J293" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K293" s="0" t="n">
         <v>1</v>
@@ -16181,7 +16181,7 @@
         <v>1.0165</v>
       </c>
       <c r="D294" s="0" t="n">
-        <v>7.412691032512314</v>
+        <v>18.062825</v>
       </c>
       <c r="E294" s="0" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>1.0135</v>
       </c>
       <c r="D295" s="0" t="n">
-        <v>5.93198992443325</v>
+        <v>14.454736</v>
       </c>
       <c r="E295" s="0" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>1.015</v>
       </c>
       <c r="D296" s="0" t="n">
-        <v>6.245943526380369</v>
+        <v>15.219761</v>
       </c>
       <c r="E296" s="0" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>1.009</v>
       </c>
       <c r="D297" s="0" t="n">
-        <v>3.552053848275862</v>
+        <v>8.655443</v>
       </c>
       <c r="E297" s="0" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>1.009</v>
       </c>
       <c r="D298" s="0" t="n">
-        <v>3.552053848275862</v>
+        <v>8.655443</v>
       </c>
       <c r="E298" s="0" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>1.009</v>
       </c>
       <c r="D299" s="0" t="n">
-        <v>3.552053848275862</v>
+        <v>8.655443</v>
       </c>
       <c r="E299" s="0" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>1.009</v>
       </c>
       <c r="D300" s="0" t="n">
-        <v>3.552053848275862</v>
+        <v>8.655443</v>
       </c>
       <c r="E300" s="0" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>1.009</v>
       </c>
       <c r="D301" s="0" t="n">
-        <v>3.552053848275862</v>
+        <v>8.655443</v>
       </c>
       <c r="E301" s="0" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>1.0105</v>
       </c>
       <c r="D302" s="0" t="n">
-        <v>4.030658730803571</v>
+        <v>9.821680000000001</v>
       </c>
       <c r="E302" s="0" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>1.0105</v>
       </c>
       <c r="D303" s="0" t="n">
-        <v>4.030658730803571</v>
+        <v>9.821680000000001</v>
       </c>
       <c r="E303" s="0" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>1.0105</v>
       </c>
       <c r="D304" s="0" t="n">
-        <v>4.030658730803571</v>
+        <v>9.821680000000001</v>
       </c>
       <c r="E304" s="0" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>1.0105</v>
       </c>
       <c r="D305" s="0" t="n">
-        <v>4.030658730803571</v>
+        <v>9.821680000000001</v>
       </c>
       <c r="E305" s="0" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>1.0105</v>
       </c>
       <c r="D306" s="0" t="n">
-        <v>4.030658730803571</v>
+        <v>9.821680000000001</v>
       </c>
       <c r="E306" s="0" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>1.012</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>6.277816224783319</v>
+        <v>15.297426</v>
       </c>
       <c r="E307" s="0" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>1.012</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>6.277816224783319</v>
+        <v>15.297426</v>
       </c>
       <c r="E308" s="0" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>1.012</v>
       </c>
       <c r="D309" s="0" t="n">
-        <v>6.277816224783319</v>
+        <v>15.297426</v>
       </c>
       <c r="E309" s="0" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>1.012</v>
       </c>
       <c r="D310" s="0" t="n">
-        <v>6.277816224783319</v>
+        <v>15.297426</v>
       </c>
       <c r="E310" s="0" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>1.012</v>
       </c>
       <c r="D311" s="0" t="n">
-        <v>6.277816224783319</v>
+        <v>15.297426</v>
       </c>
       <c r="E311" s="0" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>1.0135</v>
       </c>
       <c r="D312" s="0" t="n">
-        <v>5.93198992443325</v>
+        <v>14.454736</v>
       </c>
       <c r="E312" s="0" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>1.0135</v>
       </c>
       <c r="D313" s="0" t="n">
-        <v>5.93198992443325</v>
+        <v>14.454736</v>
       </c>
       <c r="E313" s="0" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>1.015</v>
       </c>
       <c r="D314" s="0" t="n">
-        <v>6.245943526380369</v>
+        <v>15.219761</v>
       </c>
       <c r="E314" s="0" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>1.015</v>
       </c>
       <c r="D315" s="0" t="n">
-        <v>6.245943526380369</v>
+        <v>15.219761</v>
       </c>
       <c r="E315" s="0" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>1.0165</v>
       </c>
       <c r="D316" s="0" t="n">
-        <v>7.412691032512314</v>
+        <v>18.062825</v>
       </c>
       <c r="E316" s="0" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>1.0165</v>
       </c>
       <c r="D317" s="0" t="n">
-        <v>7.412691032512314</v>
+        <v>18.062825</v>
       </c>
       <c r="E317" s="0" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>1.018</v>
       </c>
       <c r="D318" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>21.443341</v>
       </c>
       <c r="E318" s="0" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>1.018</v>
       </c>
       <c r="D319" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>21.443341</v>
       </c>
       <c r="E319" s="0" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>1.0195</v>
       </c>
       <c r="D320" s="0" t="n">
-        <v>15.13511868533171</v>
+        <v>36.880398</v>
       </c>
       <c r="E320" s="0" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>1.0195</v>
       </c>
       <c r="D321" s="0" t="n">
-        <v>15.13511868533171</v>
+        <v>36.880398</v>
       </c>
       <c r="E321" s="0" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>1.021</v>
       </c>
       <c r="D322" s="0" t="n">
-        <v>12.83957489878543</v>
+        <v>31.286748</v>
       </c>
       <c r="E322" s="0" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.021</v>
       </c>
       <c r="D323" s="0" t="n">
-        <v>12.83957489878543</v>
+        <v>31.286748</v>
       </c>
       <c r="E323" s="0" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>1.021</v>
       </c>
       <c r="D324" s="0" t="n">
-        <v>12.83957489878543</v>
+        <v>31.286748</v>
       </c>
       <c r="E324" s="0" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>1.021</v>
       </c>
       <c r="D325" s="0" t="n">
-        <v>12.83957489878543</v>
+        <v>31.286748</v>
       </c>
       <c r="E325" s="0" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>1.021</v>
       </c>
       <c r="D326" s="0" t="n">
-        <v>12.83957489878543</v>
+        <v>31.286748</v>
       </c>
       <c r="E326" s="0" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>1.0225</v>
       </c>
       <c r="D327" s="0" t="n">
-        <v>12.47008547008547</v>
+        <v>30.386397</v>
       </c>
       <c r="E327" s="0" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>1.0225</v>
       </c>
       <c r="D328" s="0" t="n">
-        <v>12.47008547008547</v>
+        <v>30.386397</v>
       </c>
       <c r="E328" s="0" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>1.024</v>
       </c>
       <c r="D329" s="0" t="n">
-        <v>14.41944194419442</v>
+        <v>35.136478</v>
       </c>
       <c r="E329" s="0" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>1.024</v>
       </c>
       <c r="D330" s="0" t="n">
-        <v>14.41944194419442</v>
+        <v>35.136478</v>
       </c>
       <c r="E330" s="0" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>1.0255</v>
       </c>
       <c r="D331" s="0" t="n">
-        <v>16.54491017964072</v>
+        <v>40.315698</v>
       </c>
       <c r="E331" s="0" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>1.0255</v>
       </c>
       <c r="D332" s="0" t="n">
-        <v>16.54491017964072</v>
+        <v>40.315698</v>
       </c>
       <c r="E332" s="0" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>1.027</v>
       </c>
       <c r="D333" s="0" t="n">
-        <v>26.6728565784275</v>
+        <v>64.99490400000001</v>
       </c>
       <c r="E333" s="0" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>1.027</v>
       </c>
       <c r="D334" s="0" t="n">
-        <v>26.6728565784275</v>
+        <v>64.99490400000001</v>
       </c>
       <c r="E334" s="0" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>1.0285</v>
       </c>
       <c r="D335" s="0" t="n">
-        <v>26.64139264990329</v>
+        <v>64.918234</v>
       </c>
       <c r="E335" s="0" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>1.0285</v>
       </c>
       <c r="D336" s="0" t="n">
-        <v>26.64139264990329</v>
+        <v>64.918234</v>
       </c>
       <c r="E336" s="0" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>1.0285</v>
       </c>
       <c r="D337" s="0" t="n">
-        <v>26.64139264990329</v>
+        <v>64.918234</v>
       </c>
       <c r="E337" s="0" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>1.0285</v>
       </c>
       <c r="D338" s="0" t="n">
-        <v>26.64139264990329</v>
+        <v>64.918234</v>
       </c>
       <c r="E338" s="0" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>1.0285</v>
       </c>
       <c r="D339" s="0" t="n">
-        <v>26.64139264990329</v>
+        <v>64.918234</v>
       </c>
       <c r="E339" s="0" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>1.03</v>
       </c>
       <c r="D340" s="0" t="n">
-        <v>25.78128440366972</v>
+        <v>62.822371</v>
       </c>
       <c r="E340" s="0" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>1.03</v>
       </c>
       <c r="D341" s="0" t="n">
-        <v>25.78128440366972</v>
+        <v>62.822371</v>
       </c>
       <c r="E341" s="0" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>1.0315</v>
       </c>
       <c r="D342" s="0" t="n">
-        <v>26.41731175228712</v>
+        <v>64.37220600000001</v>
       </c>
       <c r="E342" s="0" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>1.0315</v>
       </c>
       <c r="D343" s="0" t="n">
-        <v>26.41731175228712</v>
+        <v>64.37220600000001</v>
       </c>
       <c r="E343" s="0" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>1.033</v>
       </c>
       <c r="D344" s="0" t="n">
-        <v>29.25302826379543</v>
+        <v>71.28211899999999</v>
       </c>
       <c r="E344" s="0" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>1.033</v>
       </c>
       <c r="D345" s="0" t="n">
-        <v>29.25302826379543</v>
+        <v>71.28211899999999</v>
       </c>
       <c r="E345" s="0" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>1.0345</v>
       </c>
       <c r="D346" s="0" t="n">
-        <v>46.15486725663717</v>
+        <v>112.467562</v>
       </c>
       <c r="E346" s="0" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>1.0345</v>
       </c>
       <c r="D347" s="0" t="n">
-        <v>46.15486725663717</v>
+        <v>112.467562</v>
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>1.036</v>
       </c>
       <c r="D348" s="0" t="n">
-        <v>46.28931013051584</v>
+        <v>112.795165</v>
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>1.036</v>
       </c>
       <c r="D349" s="0" t="n">
-        <v>46.28931013051584</v>
+        <v>112.795165</v>
       </c>
       <c r="E349" s="0" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>1.0375</v>
       </c>
       <c r="D350" s="0" t="n">
-        <v>45.23578445966062</v>
+        <v>110.227993</v>
       </c>
       <c r="E350" s="0" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>1.0375</v>
       </c>
       <c r="D351" s="0" t="n">
-        <v>45.23578445966062</v>
+        <v>110.227993</v>
       </c>
       <c r="E351" s="0" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>1.039</v>
       </c>
       <c r="D352" s="0" t="n">
-        <v>44.63968894009216</v>
+        <v>108.775461</v>
       </c>
       <c r="E352" s="0" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>1.039</v>
       </c>
       <c r="D353" s="0" t="n">
-        <v>44.63968894009216</v>
+        <v>108.775461</v>
       </c>
       <c r="E353" s="0" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>1.0405</v>
       </c>
       <c r="D354" s="0" t="n">
-        <v>46.21553884711779</v>
+        <v>112.615403</v>
       </c>
       <c r="E354" s="0" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>1.0405</v>
       </c>
       <c r="D355" s="0" t="n">
-        <v>46.21553884711779</v>
+        <v>112.615403</v>
       </c>
       <c r="E355" s="0" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>1.042</v>
       </c>
       <c r="D356" s="0" t="n">
-        <v>87.55496828752644</v>
+        <v>213.348979</v>
       </c>
       <c r="E356" s="0" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>1.042</v>
       </c>
       <c r="D357" s="0" t="n">
-        <v>87.55496828752644</v>
+        <v>213.348979</v>
       </c>
       <c r="E357" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1388,10 +1388,10 @@
         <v>3260136</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>1.1066</v>
+        <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>10.373216</v>
+        <v>8</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1439,10 +1439,10 @@
         <v>3260144</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>1.1066</v>
+        <v>1.1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>10.373216</v>
+        <v>8</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1490,10 +1490,10 @@
         <v>3262136</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>1.10825</v>
+        <v>1.1</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>10.861795</v>
+        <v>10</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
         <v>3262144</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>1.10825</v>
+        <v>1.1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>10.861795</v>
+        <v>10</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>1</v>
@@ -1595,7 +1595,7 @@
         <v>1.1099</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>14.425739</v>
+        <v>13</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1.1099</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>14.425739</v>
+        <v>13</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1.05945</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>9.37673</v>
+        <v>7</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.11155</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>16.369467</v>
+        <v>15.5</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>1.11155</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>16.369467</v>
+        <v>15.5</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>1.061025</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>10.640154</v>
+        <v>9.5</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>3270107</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.12</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>14.454736</v>
+        <v>13</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         <v>3272091</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>1.015</v>
+        <v>1.18</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>15.219761</v>
+        <v>16</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2969,10 +2969,10 @@
         <v>3274115</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>18.062825</v>
+        <v>15</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         <v>3276107</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>1.018</v>
+        <v>1.3</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>21.443341</v>
+        <v>22</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>3276136</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>1.1198</v>
+        <v>1.3</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>35.738901</v>
@@ -3836,10 +3836,10 @@
         <v>3278091</v>
       </c>
       <c r="C52" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.14</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>36.880398</v>
+        <v>26</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         <v>3282091</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.08</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>30.386397</v>
+        <v>25</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4856,10 +4856,10 @@
         <v>3282107</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.08</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>30.386397</v>
+        <v>25</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -5417,10 +5417,10 @@
         <v>3284091</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>1.024</v>
+        <v>1.2</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>35.136478</v>
+        <v>32</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         <v>3284115</v>
       </c>
       <c r="C84" s="0" t="n">
-        <v>1.024</v>
+        <v>1.2</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>35.136478</v>
+        <v>32</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
         <v>3286091</v>
       </c>
       <c r="C95" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.16</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>40.315698</v>
+        <v>34</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6080,10 +6080,10 @@
         <v>3286107</v>
       </c>
       <c r="C96" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.16</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>40.315698</v>
+        <v>34</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
         <v>3286115</v>
       </c>
       <c r="C97" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.16</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>40.315698</v>
+        <v>34</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
         <v>3288091</v>
       </c>
       <c r="C108" s="0" t="n">
-        <v>1.027</v>
+        <v>1.32</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>64.99490400000001</v>
+        <v>44</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6743,10 +6743,10 @@
         <v>3288107</v>
       </c>
       <c r="C109" s="0" t="n">
-        <v>1.027</v>
+        <v>1.32</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>64.99490400000001</v>
+        <v>44</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         <v>3288115</v>
       </c>
       <c r="C110" s="0" t="n">
-        <v>1.027</v>
+        <v>1.32</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>64.99490400000001</v>
+        <v>44</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>3288709</v>
       </c>
       <c r="C118" s="0" t="n">
-        <v>0.8216</v>
+        <v>0.95</v>
       </c>
       <c r="D118" s="0" t="n">
         <v>202.567449</v>
@@ -7916,10 +7916,10 @@
         <v>3292091</v>
       </c>
       <c r="C132" s="0" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>62.822371</v>
+        <v>48</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7967,10 +7967,10 @@
         <v>3292107</v>
       </c>
       <c r="C133" s="0" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>62.822371</v>
+        <v>48</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
         <v>3292115</v>
       </c>
       <c r="C134" s="0" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>62.822371</v>
+        <v>48</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8579,10 +8579,10 @@
         <v>3294091</v>
       </c>
       <c r="C145" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.14</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>64.37220600000001</v>
+        <v>46</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8630,10 +8630,10 @@
         <v>3294107</v>
       </c>
       <c r="C146" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.14</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>64.37220600000001</v>
+        <v>46</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8681,10 +8681,10 @@
         <v>3294115</v>
       </c>
       <c r="C147" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.14</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>64.37220600000001</v>
+        <v>46</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         <v>3296091</v>
       </c>
       <c r="C158" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>71.28211899999999</v>
+        <v>55</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9293,10 +9293,10 @@
         <v>3296107</v>
       </c>
       <c r="C159" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>71.28211899999999</v>
+        <v>55</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         <v>3296115</v>
       </c>
       <c r="C160" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>71.28211899999999</v>
+        <v>55</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9956,10 +9956,10 @@
         <v>3298091</v>
       </c>
       <c r="C172" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>112.467562</v>
+        <v>65</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -10007,10 +10007,10 @@
         <v>3298107</v>
       </c>
       <c r="C173" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>112.467562</v>
+        <v>65</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10058,10 +10058,10 @@
         <v>3298115</v>
       </c>
       <c r="C174" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>112.467562</v>
+        <v>65</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10721,10 +10721,10 @@
         <v>3270091</v>
       </c>
       <c r="C187" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.12</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>14.454736</v>
+        <v>13</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10823,10 +10823,10 @@
         <v>3272115</v>
       </c>
       <c r="C189" s="0" t="n">
-        <v>1.015</v>
+        <v>1.18</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>15.219761</v>
+        <v>16</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -10925,10 +10925,10 @@
         <v>3274107</v>
       </c>
       <c r="C191" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>18.062825</v>
+        <v>15</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -11027,10 +11027,10 @@
         <v>3276091</v>
       </c>
       <c r="C193" s="0" t="n">
-        <v>1.018</v>
+        <v>1.3</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>21.443341</v>
+        <v>22</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11078,10 +11078,10 @@
         <v>3276115</v>
       </c>
       <c r="C194" s="0" t="n">
-        <v>1.018</v>
+        <v>1.3</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>21.443341</v>
+        <v>22</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11129,10 +11129,10 @@
         <v>3278107</v>
       </c>
       <c r="C195" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.14</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>36.880398</v>
+        <v>26</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11180,10 +11180,10 @@
         <v>3278115</v>
       </c>
       <c r="C196" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.14</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>36.880398</v>
+        <v>26</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
         <v>3282115</v>
       </c>
       <c r="C199" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.08</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>30.386397</v>
+        <v>25</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11486,10 +11486,10 @@
         <v>3284107</v>
       </c>
       <c r="C202" s="0" t="n">
-        <v>1.024</v>
+        <v>1.2</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>35.136478</v>
+        <v>32</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -12302,10 +12302,10 @@
         <v>10016973</v>
       </c>
       <c r="C218" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D218" s="0" t="n">
-        <v>112.795165</v>
+        <v>59</v>
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
@@ -12353,10 +12353,10 @@
         <v>10016974</v>
       </c>
       <c r="C219" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D219" s="0" t="n">
-        <v>112.795165</v>
+        <v>59</v>
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
@@ -12404,10 +12404,10 @@
         <v>10016975</v>
       </c>
       <c r="C220" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D220" s="0" t="n">
-        <v>112.795165</v>
+        <v>59</v>
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>
@@ -13067,10 +13067,10 @@
         <v>10016988</v>
       </c>
       <c r="C233" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.34</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>110.227993</v>
+        <v>75</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13118,10 +13118,10 @@
         <v>10016989</v>
       </c>
       <c r="C234" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.34</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>110.227993</v>
+        <v>75</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13169,10 +13169,10 @@
         <v>10016990</v>
       </c>
       <c r="C235" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.34</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>110.227993</v>
+        <v>75</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>10016993</v>
       </c>
       <c r="C238" s="0" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="D238" s="0" t="n">
         <v>156.156323</v>
@@ -13832,10 +13832,10 @@
         <v>10017003</v>
       </c>
       <c r="C248" s="0" t="n">
-        <v>1.039</v>
+        <v>1.18</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>108.775461</v>
+        <v>71</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
         <v>10017004</v>
       </c>
       <c r="C249" s="0" t="n">
-        <v>1.039</v>
+        <v>1.18</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>108.775461</v>
+        <v>71</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -13934,10 +13934,10 @@
         <v>10017005</v>
       </c>
       <c r="C250" s="0" t="n">
-        <v>1.039</v>
+        <v>1.18</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>108.775461</v>
+        <v>71</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -14597,10 +14597,10 @@
         <v>10017018</v>
       </c>
       <c r="C263" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.12</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>112.615403</v>
+        <v>68</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -14648,10 +14648,10 @@
         <v>10017019</v>
       </c>
       <c r="C264" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.12</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>112.615403</v>
+        <v>68</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -14699,10 +14699,10 @@
         <v>10017020</v>
       </c>
       <c r="C265" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.12</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>112.615403</v>
+        <v>68</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -15362,10 +15362,10 @@
         <v>10017033</v>
       </c>
       <c r="C278" s="0" t="n">
-        <v>1.042</v>
+        <v>1.28</v>
       </c>
       <c r="D278" s="0" t="n">
-        <v>213.348979</v>
+        <v>94</v>
       </c>
       <c r="E278" s="0" t="inlineStr">
         <is>
@@ -15413,10 +15413,10 @@
         <v>10017034</v>
       </c>
       <c r="C279" s="0" t="n">
-        <v>1.042</v>
+        <v>1.28</v>
       </c>
       <c r="D279" s="0" t="n">
-        <v>213.348979</v>
+        <v>94</v>
       </c>
       <c r="E279" s="0" t="inlineStr">
         <is>
@@ -15464,10 +15464,10 @@
         <v>10017035</v>
       </c>
       <c r="C280" s="0" t="n">
-        <v>1.042</v>
+        <v>1.28</v>
       </c>
       <c r="D280" s="0" t="n">
-        <v>213.348979</v>
+        <v>94</v>
       </c>
       <c r="E280" s="0" t="inlineStr">
         <is>
@@ -16178,10 +16178,10 @@
         <v>3274091</v>
       </c>
       <c r="C294" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D294" s="0" t="n">
-        <v>18.062825</v>
+        <v>15</v>
       </c>
       <c r="E294" s="0" t="inlineStr">
         <is>
@@ -16229,10 +16229,10 @@
         <v>3270115</v>
       </c>
       <c r="C295" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.12</v>
       </c>
       <c r="D295" s="0" t="n">
-        <v>14.454736</v>
+        <v>13</v>
       </c>
       <c r="E295" s="0" t="inlineStr">
         <is>
@@ -16280,10 +16280,10 @@
         <v>3272107</v>
       </c>
       <c r="C296" s="0" t="n">
-        <v>1.015</v>
+        <v>1.18</v>
       </c>
       <c r="D296" s="0" t="n">
-        <v>15.219761</v>
+        <v>16</v>
       </c>
       <c r="E296" s="0" t="inlineStr">
         <is>
@@ -16841,10 +16841,10 @@
         <v>3268019</v>
       </c>
       <c r="C307" s="0" t="n">
-        <v>1.012</v>
+        <v>1.05</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>15.297426</v>
+        <v>11</v>
       </c>
       <c r="E307" s="0" t="inlineStr">
         <is>
@@ -16892,10 +16892,10 @@
         <v>3268091</v>
       </c>
       <c r="C308" s="0" t="n">
-        <v>1.012</v>
+        <v>1.05</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>15.297426</v>
+        <v>11</v>
       </c>
       <c r="E308" s="0" t="inlineStr">
         <is>
@@ -16943,10 +16943,10 @@
         <v>3268099</v>
       </c>
       <c r="C309" s="0" t="n">
-        <v>1.012</v>
+        <v>1.05</v>
       </c>
       <c r="D309" s="0" t="n">
-        <v>15.297426</v>
+        <v>11</v>
       </c>
       <c r="E309" s="0" t="inlineStr">
         <is>
@@ -16994,10 +16994,10 @@
         <v>3268107</v>
       </c>
       <c r="C310" s="0" t="n">
-        <v>1.012</v>
+        <v>1.05</v>
       </c>
       <c r="D310" s="0" t="n">
-        <v>15.297426</v>
+        <v>11</v>
       </c>
       <c r="E310" s="0" t="inlineStr">
         <is>
@@ -17045,10 +17045,10 @@
         <v>3268115</v>
       </c>
       <c r="C311" s="0" t="n">
-        <v>1.012</v>
+        <v>1.05</v>
       </c>
       <c r="D311" s="0" t="n">
-        <v>15.297426</v>
+        <v>11</v>
       </c>
       <c r="E311" s="0" t="inlineStr">
         <is>
@@ -17096,10 +17096,10 @@
         <v>3270019</v>
       </c>
       <c r="C312" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.12</v>
       </c>
       <c r="D312" s="0" t="n">
-        <v>14.454736</v>
+        <v>13</v>
       </c>
       <c r="E312" s="0" t="inlineStr">
         <is>
@@ -17147,10 +17147,10 @@
         <v>3270099</v>
       </c>
       <c r="C313" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.12</v>
       </c>
       <c r="D313" s="0" t="n">
-        <v>14.454736</v>
+        <v>13</v>
       </c>
       <c r="E313" s="0" t="inlineStr">
         <is>
@@ -17198,10 +17198,10 @@
         <v>3272019</v>
       </c>
       <c r="C314" s="0" t="n">
-        <v>1.015</v>
+        <v>1.18</v>
       </c>
       <c r="D314" s="0" t="n">
-        <v>15.219761</v>
+        <v>16</v>
       </c>
       <c r="E314" s="0" t="inlineStr">
         <is>
@@ -17249,10 +17249,10 @@
         <v>3272099</v>
       </c>
       <c r="C315" s="0" t="n">
-        <v>1.015</v>
+        <v>1.18</v>
       </c>
       <c r="D315" s="0" t="n">
-        <v>15.219761</v>
+        <v>16</v>
       </c>
       <c r="E315" s="0" t="inlineStr">
         <is>
@@ -17300,10 +17300,10 @@
         <v>3274019</v>
       </c>
       <c r="C316" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D316" s="0" t="n">
-        <v>18.062825</v>
+        <v>15</v>
       </c>
       <c r="E316" s="0" t="inlineStr">
         <is>
@@ -17351,10 +17351,10 @@
         <v>3274099</v>
       </c>
       <c r="C317" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D317" s="0" t="n">
-        <v>18.062825</v>
+        <v>15</v>
       </c>
       <c r="E317" s="0" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>3276019</v>
       </c>
       <c r="C318" s="0" t="n">
-        <v>1.018</v>
+        <v>1.3</v>
       </c>
       <c r="D318" s="0" t="n">
-        <v>21.443341</v>
+        <v>22</v>
       </c>
       <c r="E318" s="0" t="inlineStr">
         <is>
@@ -17453,10 +17453,10 @@
         <v>3276099</v>
       </c>
       <c r="C319" s="0" t="n">
-        <v>1.018</v>
+        <v>1.3</v>
       </c>
       <c r="D319" s="0" t="n">
-        <v>21.443341</v>
+        <v>22</v>
       </c>
       <c r="E319" s="0" t="inlineStr">
         <is>
@@ -17504,10 +17504,10 @@
         <v>3278019</v>
       </c>
       <c r="C320" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.14</v>
       </c>
       <c r="D320" s="0" t="n">
-        <v>36.880398</v>
+        <v>26</v>
       </c>
       <c r="E320" s="0" t="inlineStr">
         <is>
@@ -17555,10 +17555,10 @@
         <v>3278099</v>
       </c>
       <c r="C321" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.14</v>
       </c>
       <c r="D321" s="0" t="n">
-        <v>36.880398</v>
+        <v>26</v>
       </c>
       <c r="E321" s="0" t="inlineStr">
         <is>
@@ -17606,10 +17606,10 @@
         <v>3280019</v>
       </c>
       <c r="C322" s="0" t="n">
-        <v>1.021</v>
+        <v>1.18</v>
       </c>
       <c r="D322" s="0" t="n">
-        <v>31.286748</v>
+        <v>29</v>
       </c>
       <c r="E322" s="0" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         <v>3280091</v>
       </c>
       <c r="C323" s="0" t="n">
-        <v>1.021</v>
+        <v>1.18</v>
       </c>
       <c r="D323" s="0" t="n">
-        <v>31.286748</v>
+        <v>29</v>
       </c>
       <c r="E323" s="0" t="inlineStr">
         <is>
@@ -17708,10 +17708,10 @@
         <v>3280099</v>
       </c>
       <c r="C324" s="0" t="n">
-        <v>1.021</v>
+        <v>1.18</v>
       </c>
       <c r="D324" s="0" t="n">
-        <v>31.286748</v>
+        <v>29</v>
       </c>
       <c r="E324" s="0" t="inlineStr">
         <is>
@@ -17759,10 +17759,10 @@
         <v>3280107</v>
       </c>
       <c r="C325" s="0" t="n">
-        <v>1.021</v>
+        <v>1.18</v>
       </c>
       <c r="D325" s="0" t="n">
-        <v>31.286748</v>
+        <v>29</v>
       </c>
       <c r="E325" s="0" t="inlineStr">
         <is>
@@ -17810,10 +17810,10 @@
         <v>3280115</v>
       </c>
       <c r="C326" s="0" t="n">
-        <v>1.021</v>
+        <v>1.18</v>
       </c>
       <c r="D326" s="0" t="n">
-        <v>31.286748</v>
+        <v>29</v>
       </c>
       <c r="E326" s="0" t="inlineStr">
         <is>
@@ -17861,10 +17861,10 @@
         <v>3282019</v>
       </c>
       <c r="C327" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.08</v>
       </c>
       <c r="D327" s="0" t="n">
-        <v>30.386397</v>
+        <v>25</v>
       </c>
       <c r="E327" s="0" t="inlineStr">
         <is>
@@ -17912,10 +17912,10 @@
         <v>3282099</v>
       </c>
       <c r="C328" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.08</v>
       </c>
       <c r="D328" s="0" t="n">
-        <v>30.386397</v>
+        <v>25</v>
       </c>
       <c r="E328" s="0" t="inlineStr">
         <is>
@@ -17963,10 +17963,10 @@
         <v>3284019</v>
       </c>
       <c r="C329" s="0" t="n">
-        <v>1.024</v>
+        <v>1.2</v>
       </c>
       <c r="D329" s="0" t="n">
-        <v>35.136478</v>
+        <v>32</v>
       </c>
       <c r="E329" s="0" t="inlineStr">
         <is>
@@ -18014,10 +18014,10 @@
         <v>3284099</v>
       </c>
       <c r="C330" s="0" t="n">
-        <v>1.024</v>
+        <v>1.2</v>
       </c>
       <c r="D330" s="0" t="n">
-        <v>35.136478</v>
+        <v>32</v>
       </c>
       <c r="E330" s="0" t="inlineStr">
         <is>
@@ -18065,10 +18065,10 @@
         <v>3286019</v>
       </c>
       <c r="C331" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.16</v>
       </c>
       <c r="D331" s="0" t="n">
-        <v>40.315698</v>
+        <v>34</v>
       </c>
       <c r="E331" s="0" t="inlineStr">
         <is>
@@ -18116,10 +18116,10 @@
         <v>3286099</v>
       </c>
       <c r="C332" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.16</v>
       </c>
       <c r="D332" s="0" t="n">
-        <v>40.315698</v>
+        <v>34</v>
       </c>
       <c r="E332" s="0" t="inlineStr">
         <is>
@@ -18167,10 +18167,10 @@
         <v>3288019</v>
       </c>
       <c r="C333" s="0" t="n">
-        <v>1.027</v>
+        <v>1.32</v>
       </c>
       <c r="D333" s="0" t="n">
-        <v>64.99490400000001</v>
+        <v>44</v>
       </c>
       <c r="E333" s="0" t="inlineStr">
         <is>
@@ -18218,10 +18218,10 @@
         <v>3288099</v>
       </c>
       <c r="C334" s="0" t="n">
-        <v>1.027</v>
+        <v>1.32</v>
       </c>
       <c r="D334" s="0" t="n">
-        <v>64.99490400000001</v>
+        <v>44</v>
       </c>
       <c r="E334" s="0" t="inlineStr">
         <is>
@@ -18269,10 +18269,10 @@
         <v>3290019</v>
       </c>
       <c r="C335" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.1</v>
       </c>
       <c r="D335" s="0" t="n">
-        <v>64.918234</v>
+        <v>40</v>
       </c>
       <c r="E335" s="0" t="inlineStr">
         <is>
@@ -18320,10 +18320,10 @@
         <v>3290091</v>
       </c>
       <c r="C336" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.1</v>
       </c>
       <c r="D336" s="0" t="n">
-        <v>64.918234</v>
+        <v>40</v>
       </c>
       <c r="E336" s="0" t="inlineStr">
         <is>
@@ -18371,10 +18371,10 @@
         <v>3290099</v>
       </c>
       <c r="C337" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.1</v>
       </c>
       <c r="D337" s="0" t="n">
-        <v>64.918234</v>
+        <v>40</v>
       </c>
       <c r="E337" s="0" t="inlineStr">
         <is>
@@ -18422,10 +18422,10 @@
         <v>3290107</v>
       </c>
       <c r="C338" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.1</v>
       </c>
       <c r="D338" s="0" t="n">
-        <v>64.918234</v>
+        <v>40</v>
       </c>
       <c r="E338" s="0" t="inlineStr">
         <is>
@@ -18473,10 +18473,10 @@
         <v>3290115</v>
       </c>
       <c r="C339" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.1</v>
       </c>
       <c r="D339" s="0" t="n">
-        <v>64.918234</v>
+        <v>40</v>
       </c>
       <c r="E339" s="0" t="inlineStr">
         <is>
@@ -18524,10 +18524,10 @@
         <v>3292019</v>
       </c>
       <c r="C340" s="0" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="D340" s="0" t="n">
-        <v>62.822371</v>
+        <v>48</v>
       </c>
       <c r="E340" s="0" t="inlineStr">
         <is>
@@ -18575,10 +18575,10 @@
         <v>3292099</v>
       </c>
       <c r="C341" s="0" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="D341" s="0" t="n">
-        <v>62.822371</v>
+        <v>48</v>
       </c>
       <c r="E341" s="0" t="inlineStr">
         <is>
@@ -18626,10 +18626,10 @@
         <v>3294019</v>
       </c>
       <c r="C342" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.14</v>
       </c>
       <c r="D342" s="0" t="n">
-        <v>64.37220600000001</v>
+        <v>46</v>
       </c>
       <c r="E342" s="0" t="inlineStr">
         <is>
@@ -18677,10 +18677,10 @@
         <v>3294099</v>
       </c>
       <c r="C343" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.14</v>
       </c>
       <c r="D343" s="0" t="n">
-        <v>64.37220600000001</v>
+        <v>46</v>
       </c>
       <c r="E343" s="0" t="inlineStr">
         <is>
@@ -18728,10 +18728,10 @@
         <v>3296019</v>
       </c>
       <c r="C344" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D344" s="0" t="n">
-        <v>71.28211899999999</v>
+        <v>55</v>
       </c>
       <c r="E344" s="0" t="inlineStr">
         <is>
@@ -18779,10 +18779,10 @@
         <v>3296099</v>
       </c>
       <c r="C345" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D345" s="0" t="n">
-        <v>71.28211899999999</v>
+        <v>55</v>
       </c>
       <c r="E345" s="0" t="inlineStr">
         <is>
@@ -18830,10 +18830,10 @@
         <v>3298019</v>
       </c>
       <c r="C346" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D346" s="0" t="n">
-        <v>112.467562</v>
+        <v>65</v>
       </c>
       <c r="E346" s="0" t="inlineStr">
         <is>
@@ -18881,10 +18881,10 @@
         <v>3298099</v>
       </c>
       <c r="C347" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D347" s="0" t="n">
-        <v>112.467562</v>
+        <v>65</v>
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
@@ -18932,10 +18932,10 @@
         <v>10048510</v>
       </c>
       <c r="C348" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D348" s="0" t="n">
-        <v>112.795165</v>
+        <v>59</v>
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
@@ -18983,10 +18983,10 @@
         <v>10048511</v>
       </c>
       <c r="C349" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D349" s="0" t="n">
-        <v>112.795165</v>
+        <v>59</v>
       </c>
       <c r="E349" s="0" t="inlineStr">
         <is>
@@ -19034,10 +19034,10 @@
         <v>10048512</v>
       </c>
       <c r="C350" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.34</v>
       </c>
       <c r="D350" s="0" t="n">
-        <v>110.227993</v>
+        <v>75</v>
       </c>
       <c r="E350" s="0" t="inlineStr">
         <is>
@@ -19085,10 +19085,10 @@
         <v>10048513</v>
       </c>
       <c r="C351" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.34</v>
       </c>
       <c r="D351" s="0" t="n">
-        <v>110.227993</v>
+        <v>75</v>
       </c>
       <c r="E351" s="0" t="inlineStr">
         <is>
@@ -19136,10 +19136,10 @@
         <v>10048514</v>
       </c>
       <c r="C352" s="0" t="n">
-        <v>1.039</v>
+        <v>1.18</v>
       </c>
       <c r="D352" s="0" t="n">
-        <v>108.775461</v>
+        <v>71</v>
       </c>
       <c r="E352" s="0" t="inlineStr">
         <is>
@@ -19187,10 +19187,10 @@
         <v>10048515</v>
       </c>
       <c r="C353" s="0" t="n">
-        <v>1.039</v>
+        <v>1.18</v>
       </c>
       <c r="D353" s="0" t="n">
-        <v>108.775461</v>
+        <v>71</v>
       </c>
       <c r="E353" s="0" t="inlineStr">
         <is>
@@ -19238,10 +19238,10 @@
         <v>10048516</v>
       </c>
       <c r="C354" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.12</v>
       </c>
       <c r="D354" s="0" t="n">
-        <v>112.615403</v>
+        <v>68</v>
       </c>
       <c r="E354" s="0" t="inlineStr">
         <is>
@@ -19289,10 +19289,10 @@
         <v>10048517</v>
       </c>
       <c r="C355" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.12</v>
       </c>
       <c r="D355" s="0" t="n">
-        <v>112.615403</v>
+        <v>68</v>
       </c>
       <c r="E355" s="0" t="inlineStr">
         <is>
@@ -19340,10 +19340,10 @@
         <v>10048518</v>
       </c>
       <c r="C356" s="0" t="n">
-        <v>1.042</v>
+        <v>1.28</v>
       </c>
       <c r="D356" s="0" t="n">
-        <v>213.348979</v>
+        <v>94</v>
       </c>
       <c r="E356" s="0" t="inlineStr">
         <is>
@@ -19391,10 +19391,10 @@
         <v>10048519</v>
       </c>
       <c r="C357" s="0" t="n">
-        <v>1.042</v>
+        <v>1.28</v>
       </c>
       <c r="D357" s="0" t="n">
-        <v>213.348979</v>
+        <v>94</v>
       </c>
       <c r="E357" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L05/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P357"/>
+  <dimension ref="A1:Q357"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -1140,6 +1140,7 @@
     <col width="9" customWidth="1" style="2" min="13" max="14"/>
     <col width="17.3333333333333" customWidth="1" style="2" min="15" max="15"/>
     <col width="9" customWidth="1" style="2" min="16" max="16384"/>
+    <col width="10" customWidth="1" style="2" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,6 +1224,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>levelId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1272,37 +1278,42 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -1380,6 +1391,11 @@
       <c r="P3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>所属关卡 id（本表每关独立一份，2026-10-30 拆分）</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1449,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=1</t>
         </is>
       </c>
+      <c r="Q4" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="n">
@@ -1484,6 +1503,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=1</t>
         </is>
       </c>
+      <c r="Q5" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -1535,6 +1557,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=2</t>
         </is>
       </c>
+      <c r="Q6" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="B7" s="0" t="n">
@@ -1586,6 +1611,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=2</t>
         </is>
       </c>
+      <c r="Q7" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="B8" s="0" t="n">
@@ -1637,6 +1665,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q8" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="B9" s="0" t="n">
@@ -1688,6 +1719,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q9" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="B10" s="0" t="n">
@@ -1739,6 +1773,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q10" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="B11" s="0" t="n">
@@ -1790,6 +1827,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q11" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -1841,6 +1881,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q12" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
@@ -1892,6 +1935,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q13" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -1943,6 +1989,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q14" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -1994,6 +2043,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q15" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
@@ -2045,6 +2097,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q16" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -2096,6 +2151,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q17" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="n">
@@ -2147,6 +2205,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q18" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="n">
@@ -2198,6 +2259,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q19" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -2249,6 +2313,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q20" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
@@ -2300,6 +2367,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q21" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
@@ -2351,6 +2421,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q22" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
@@ -2402,6 +2475,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q23" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="n">
@@ -2453,6 +2529,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q24" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
@@ -2504,6 +2583,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q25" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
@@ -2555,6 +2637,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q26" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
@@ -2606,6 +2691,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q27" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
@@ -2657,6 +2745,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q28" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="n">
@@ -2708,6 +2799,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q29" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="n">
@@ -2759,6 +2853,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q30" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="n">
@@ -2810,6 +2907,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q31" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="n">
@@ -2861,6 +2961,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q32" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="n">
@@ -2912,6 +3015,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q33" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="n">
@@ -2963,6 +3069,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q34" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n">
@@ -3014,6 +3123,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q35" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="n">
@@ -3065,6 +3177,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q36" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="n">
@@ -3116,6 +3231,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q37" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="n">
@@ -3167,6 +3285,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q38" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="n">
@@ -3218,6 +3339,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q39" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="n">
@@ -3269,6 +3393,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q40" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="n">
@@ -3320,6 +3447,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q41" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="n">
@@ -3371,6 +3501,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q42" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="n">
@@ -3422,6 +3555,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q43" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="n">
@@ -3473,6 +3609,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q44" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="n">
@@ -3524,6 +3663,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q45" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="n">
@@ -3575,6 +3717,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q46" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="n">
@@ -3626,6 +3771,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q47" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="n">
@@ -3677,6 +3825,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q48" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="n">
@@ -3728,6 +3879,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q49" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="n">
@@ -3779,6 +3933,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q50" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="n">
@@ -3830,6 +3987,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q51" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="n">
@@ -3881,6 +4041,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q52" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="n">
@@ -3932,6 +4095,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q53" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="n">
@@ -3983,6 +4149,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q54" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="0" t="n">
@@ -4034,6 +4203,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q55" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="0" t="n">
@@ -4085,6 +4257,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q56" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="n">
@@ -4136,6 +4311,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q57" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="n">
@@ -4187,6 +4365,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q58" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="n">
@@ -4238,6 +4419,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q59" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="0" t="n">
@@ -4289,6 +4473,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q60" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="0" t="n">
@@ -4340,6 +4527,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q61" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="n">
@@ -4391,6 +4581,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q62" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="0" t="n">
@@ -4442,6 +4635,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q63" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="n">
@@ -4493,6 +4689,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q64" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="n">
@@ -4544,6 +4743,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q65" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="0" t="n">
@@ -4595,6 +4797,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q66" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="0" t="n">
@@ -4646,6 +4851,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q67" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="n">
@@ -4697,6 +4905,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q68" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="0" t="n">
@@ -4748,6 +4959,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q69" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="0" t="n">
@@ -4799,6 +5013,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q70" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="0" t="n">
@@ -4850,6 +5067,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q71" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="0" t="n">
@@ -4901,6 +5121,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q72" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="0" t="n">
@@ -4952,6 +5175,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q73" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="0" t="n">
@@ -5003,6 +5229,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q74" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="0" t="n">
@@ -5054,6 +5283,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q75" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="n">
@@ -5105,6 +5337,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q76" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="n">
@@ -5156,6 +5391,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q77" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="n">
@@ -5207,6 +5445,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q78" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="0" t="n">
@@ -5258,6 +5499,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q79" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="0" t="n">
@@ -5309,6 +5553,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q80" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="n">
@@ -5360,6 +5607,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q81" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="n">
@@ -5411,6 +5661,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q82" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="n">
@@ -5462,6 +5715,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q83" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="n">
@@ -5513,6 +5769,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q84" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="n">
@@ -5564,6 +5823,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q85" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="n">
@@ -5615,6 +5877,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q86" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="n">
@@ -5666,6 +5931,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q87" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="n">
@@ -5717,6 +5985,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q88" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="n">
@@ -5768,6 +6039,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q89" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="n">
@@ -5819,6 +6093,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q90" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="n">
@@ -5870,6 +6147,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q91" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="n">
@@ -5921,6 +6201,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q92" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="n">
@@ -5972,6 +6255,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q93" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="n">
@@ -6023,6 +6309,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q94" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="n">
@@ -6074,6 +6363,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q95" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="0" t="n">
@@ -6125,6 +6417,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q96" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="n">
@@ -6176,6 +6471,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q97" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="n">
@@ -6227,6 +6525,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q98" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="n">
@@ -6278,6 +6579,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q99" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="0" t="n">
@@ -6329,6 +6633,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q100" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="0" t="n">
@@ -6380,6 +6687,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q101" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="0" t="n">
@@ -6431,6 +6741,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q102" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="0" t="n">
@@ -6482,6 +6795,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q103" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="0" t="n">
@@ -6533,6 +6849,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q104" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="0" t="n">
@@ -6584,6 +6903,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q105" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="0" t="n">
@@ -6635,6 +6957,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q106" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="0" t="n">
@@ -6686,6 +7011,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q107" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="0" t="n">
@@ -6737,6 +7065,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q108" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="0" t="n">
@@ -6788,6 +7119,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q109" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="110">
       <c r="B110" s="0" t="n">
@@ -6839,6 +7173,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q110" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="0" t="n">
@@ -6890,6 +7227,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q111" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="0" t="n">
@@ -6941,6 +7281,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q112" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="0" t="n">
@@ -6992,6 +7335,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q113" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="0" t="n">
@@ -7043,6 +7389,9 @@
           <t>Balance variant; canonical=31; role=elite; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q114" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="0" t="n">
@@ -7094,6 +7443,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q115" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="116">
       <c r="B116" s="0" t="n">
@@ -7145,6 +7497,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q116" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="117">
       <c r="B117" s="0" t="n">
@@ -7196,6 +7551,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q117" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="0" t="n">
@@ -7247,6 +7605,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q118" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119">
       <c r="B119" s="0" t="n">
@@ -7298,6 +7659,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q119" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="120">
       <c r="B120" s="0" t="n">
@@ -7349,6 +7713,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q120" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="0" t="n">
@@ -7400,6 +7767,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q121" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="0" t="n">
@@ -7451,6 +7821,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q122" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="123">
       <c r="B123" s="0" t="n">
@@ -7502,6 +7875,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q123" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="124">
       <c r="B124" s="0" t="n">
@@ -7553,6 +7929,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q124" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="125">
       <c r="B125" s="0" t="n">
@@ -7604,6 +7983,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q125" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="126">
       <c r="B126" s="0" t="n">
@@ -7655,6 +8037,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q126" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="127">
       <c r="B127" s="0" t="n">
@@ -7706,6 +8091,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q127" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="128">
       <c r="B128" s="0" t="n">
@@ -7757,6 +8145,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q128" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="129">
       <c r="B129" s="0" t="n">
@@ -7808,6 +8199,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q129" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="130">
       <c r="B130" s="0" t="n">
@@ -7859,6 +8253,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q130" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="131">
       <c r="B131" s="0" t="n">
@@ -7910,6 +8307,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q131" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="132">
       <c r="B132" s="0" t="n">
@@ -7961,6 +8361,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q132" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="133">
       <c r="B133" s="0" t="n">
@@ -8012,6 +8415,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q133" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="134">
       <c r="B134" s="0" t="n">
@@ -8063,6 +8469,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q134" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="0" t="n">
@@ -8114,6 +8523,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q135" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="0" t="n">
@@ -8165,6 +8577,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q136" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="n">
@@ -8216,6 +8631,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q137" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="138">
       <c r="B138" s="0" t="n">
@@ -8267,6 +8685,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q138" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="139">
       <c r="B139" s="0" t="n">
@@ -8318,6 +8739,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q139" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="140">
       <c r="B140" s="0" t="n">
@@ -8369,6 +8793,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q140" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="0" t="n">
@@ -8420,6 +8847,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q141" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="0" t="n">
@@ -8471,6 +8901,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q142" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="0" t="n">
@@ -8522,6 +8955,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q143" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="0" t="n">
@@ -8573,6 +9009,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q144" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="0" t="n">
@@ -8624,6 +9063,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q145" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="146">
       <c r="B146" s="0" t="n">
@@ -8675,6 +9117,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q146" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="0" t="n">
@@ -8726,6 +9171,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q147" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="B148" s="0" t="n">
@@ -8777,6 +9225,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q148" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="0" t="n">
@@ -8828,6 +9279,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q149" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="0" t="n">
@@ -8879,6 +9333,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q150" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="0" t="n">
@@ -8930,6 +9387,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q151" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="0" t="n">
@@ -8981,6 +9441,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q152" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="0" t="n">
@@ -9032,6 +9495,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q153" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="0" t="n">
@@ -9083,6 +9549,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q154" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="155">
       <c r="B155" s="0" t="n">
@@ -9134,6 +9603,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q155" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="156">
       <c r="B156" s="0" t="n">
@@ -9185,6 +9657,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q156" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="0" t="n">
@@ -9236,6 +9711,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q157" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="0" t="n">
@@ -9287,6 +9765,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q158" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="0" t="n">
@@ -9338,6 +9819,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q159" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="0" t="n">
@@ -9389,6 +9873,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q160" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="161">
       <c r="B161" s="0" t="n">
@@ -9440,6 +9927,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q161" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="162">
       <c r="B162" s="0" t="n">
@@ -9491,6 +9981,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q162" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="163">
       <c r="B163" s="0" t="n">
@@ -9542,6 +10035,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q163" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="0" t="n">
@@ -9593,6 +10089,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q164" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="165">
       <c r="B165" s="0" t="n">
@@ -9644,6 +10143,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q165" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="166">
       <c r="B166" s="0" t="n">
@@ -9695,6 +10197,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q166" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="0" t="n">
@@ -9746,6 +10251,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q167" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="168">
       <c r="B168" s="0" t="n">
@@ -9797,6 +10305,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q168" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="169">
       <c r="B169" s="0" t="n">
@@ -9848,6 +10359,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q169" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="170">
       <c r="B170" s="0" t="n">
@@ -9899,6 +10413,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q170" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="171">
       <c r="B171" s="0" t="n">
@@ -9950,6 +10467,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q171" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="172">
       <c r="B172" s="0" t="n">
@@ -10001,6 +10521,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q172" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="173">
       <c r="B173" s="0" t="n">
@@ -10052,6 +10575,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q173" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="174">
       <c r="B174" s="0" t="n">
@@ -10103,6 +10629,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q174" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="0" t="n">
@@ -10154,6 +10683,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q175" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="176">
       <c r="B176" s="0" t="n">
@@ -10205,6 +10737,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q176" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="0" t="n">
@@ -10256,6 +10791,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q177" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="178">
       <c r="B178" s="0" t="n">
@@ -10307,6 +10845,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q178" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="179">
       <c r="B179" s="0" t="n">
@@ -10358,6 +10899,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q179" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="180">
       <c r="B180" s="0" t="n">
@@ -10409,6 +10953,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q180" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="181">
       <c r="B181" s="0" t="n">
@@ -10460,6 +11007,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q181" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="182">
       <c r="B182" s="0" t="n">
@@ -10511,6 +11061,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q182" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="183">
       <c r="B183" s="0" t="n">
@@ -10562,6 +11115,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q183" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="184">
       <c r="B184" s="0" t="n">
@@ -10613,6 +11169,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q184" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="185">
       <c r="B185" s="0" t="n">
@@ -10664,6 +11223,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q185" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="186">
       <c r="B186" s="0" t="n">
@@ -10715,6 +11277,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q186" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="187">
       <c r="B187" s="0" t="n">
@@ -10766,6 +11331,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q187" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="188">
       <c r="B188" s="0" t="n">
@@ -10817,6 +11385,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q188" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="189">
       <c r="B189" s="0" t="n">
@@ -10868,6 +11439,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q189" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="190">
       <c r="B190" s="0" t="n">
@@ -10919,6 +11493,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q190" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="191">
       <c r="B191" s="0" t="n">
@@ -10970,6 +11547,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q191" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="192">
       <c r="B192" s="0" t="n">
@@ -11021,6 +11601,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q192" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="193">
       <c r="B193" s="0" t="n">
@@ -11072,6 +11655,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q193" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="194">
       <c r="B194" s="0" t="n">
@@ -11123,6 +11709,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q194" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="195">
       <c r="B195" s="0" t="n">
@@ -11174,6 +11763,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q195" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="196">
       <c r="B196" s="0" t="n">
@@ -11225,6 +11817,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q196" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="197">
       <c r="B197" s="0" t="n">
@@ -11276,6 +11871,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q197" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="198">
       <c r="B198" s="0" t="n">
@@ -11327,6 +11925,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q198" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="199">
       <c r="B199" s="0" t="n">
@@ -11378,6 +11979,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q199" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="200">
       <c r="B200" s="0" t="n">
@@ -11429,6 +12033,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q200" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201">
       <c r="B201" s="0" t="n">
@@ -11480,6 +12087,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q201" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="202">
       <c r="B202" s="0" t="n">
@@ -11531,6 +12141,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q202" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="203">
       <c r="B203" s="0" t="n">
@@ -11582,6 +12195,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q203" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="204">
       <c r="B204" s="0" t="n">
@@ -11633,6 +12249,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q204" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="205">
       <c r="B205" s="0" t="n">
@@ -11684,6 +12303,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q205" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="n">
@@ -11735,6 +12357,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q206" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="n">
@@ -11786,6 +12411,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q207" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="n">
@@ -11837,6 +12465,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q208" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="n">
@@ -11888,6 +12519,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q209" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="n">
@@ -11939,6 +12573,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q210" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="n">
@@ -11990,6 +12627,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q211" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="212">
       <c r="B212" s="0" t="n">
@@ -12041,6 +12681,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q212" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="n">
@@ -12092,6 +12735,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q213" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="n">
@@ -12143,6 +12789,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q214" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="n">
@@ -12194,6 +12843,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q215" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="n">
@@ -12245,6 +12897,9 @@
           <t>Balance variant; canonical=31; role=elite; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q216" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="n">
@@ -12296,6 +12951,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q217" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="n">
@@ -12347,6 +13005,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q218" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="n">
@@ -12398,6 +13059,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q219" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="n">
@@ -12449,6 +13113,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q220" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="n">
@@ -12500,6 +13167,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q221" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="n">
@@ -12551,6 +13221,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q222" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="n">
@@ -12602,6 +13275,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q223" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="n">
@@ -12653,6 +13329,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q224" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="n">
@@ -12704,6 +13383,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q225" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="n">
@@ -12755,6 +13437,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q226" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="n">
@@ -12806,6 +13491,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q227" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="n">
@@ -12857,6 +13545,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q228" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="n">
@@ -12908,6 +13599,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q229" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="n">
@@ -12959,6 +13653,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q230" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="n">
@@ -13010,6 +13707,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q231" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="n">
@@ -13061,6 +13761,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q232" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="n">
@@ -13112,6 +13815,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q233" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="n">
@@ -13163,6 +13869,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q234" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="n">
@@ -13214,6 +13923,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q235" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="n">
@@ -13265,6 +13977,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q236" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="n">
@@ -13316,6 +14031,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q237" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="n">
@@ -13367,6 +14085,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q238" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="n">
@@ -13418,6 +14139,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q239" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="n">
@@ -13469,6 +14193,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q240" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="n">
@@ -13520,6 +14247,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q241" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="n">
@@ -13571,6 +14301,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q242" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="n">
@@ -13622,6 +14355,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q243" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="n">
@@ -13673,6 +14409,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q244" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="n">
@@ -13724,6 +14463,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q245" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="n">
@@ -13775,6 +14517,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q246" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="n">
@@ -13826,6 +14571,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q247" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="n">
@@ -13877,6 +14625,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q248" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="n">
@@ -13928,6 +14679,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q249" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="n">
@@ -13979,6 +14733,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q250" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="n">
@@ -14030,6 +14787,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q251" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="n">
@@ -14081,6 +14841,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q252" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="n">
@@ -14132,6 +14895,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q253" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="n">
@@ -14183,6 +14949,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q254" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="n">
@@ -14234,6 +15003,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q255" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="n">
@@ -14285,6 +15057,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q256" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="n">
@@ -14336,6 +15111,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q257" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="n">
@@ -14387,6 +15165,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q258" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="n">
@@ -14438,6 +15219,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q259" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="n">
@@ -14489,6 +15273,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q260" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="n">
@@ -14540,6 +15327,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q261" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="n">
@@ -14591,6 +15381,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q262" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="n">
@@ -14642,6 +15435,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q263" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="n">
@@ -14693,6 +15489,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q264" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="n">
@@ -14744,6 +15543,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q265" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="n">
@@ -14795,6 +15597,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q266" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="n">
@@ -14846,6 +15651,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q267" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="n">
@@ -14897,6 +15705,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q268" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="n">
@@ -14948,6 +15759,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q269" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="n">
@@ -14999,6 +15813,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q270" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="n">
@@ -15050,6 +15867,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q271" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="n">
@@ -15101,6 +15921,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q272" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="n">
@@ -15152,6 +15975,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q273" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="n">
@@ -15203,6 +16029,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q274" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="n">
@@ -15254,6 +16083,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q275" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="n">
@@ -15305,6 +16137,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q276" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="n">
@@ -15356,6 +16191,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q277" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="n">
@@ -15407,6 +16245,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q278" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="n">
@@ -15458,6 +16299,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q279" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="n">
@@ -15509,6 +16353,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q280" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="n">
@@ -15560,6 +16407,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q281" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="n">
@@ -15611,6 +16461,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q282" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="n">
@@ -15662,6 +16515,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q283" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="n">
@@ -15713,6 +16569,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q284" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="n">
@@ -15764,6 +16623,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q285" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="n">
@@ -15815,6 +16677,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q286" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="n">
@@ -15866,6 +16731,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q287" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="n">
@@ -15917,6 +16785,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q288" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="n">
@@ -15968,6 +16839,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q289" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="n">
@@ -16019,6 +16893,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q290" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="n">
@@ -16070,6 +16947,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q291" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="n">
@@ -16121,6 +17001,9 @@
           <t>Balance variant; canonical=123; role=elite; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q292" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="n">
@@ -16172,6 +17055,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q293" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="n">
@@ -16223,6 +17109,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q294" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="n">
@@ -16274,6 +17163,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q295" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="n">
@@ -16325,6 +17217,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q296" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="n">
@@ -16376,6 +17271,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q297" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="n">
@@ -16427,6 +17325,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q298" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="n">
@@ -16478,6 +17379,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q299" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="n">
@@ -16529,6 +17433,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q300" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="301">
       <c r="B301" s="0" t="n">
@@ -16580,6 +17487,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=3</t>
         </is>
       </c>
+      <c r="Q301" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="302">
       <c r="B302" s="0" t="n">
@@ -16631,6 +17541,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q302" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="303">
       <c r="B303" s="0" t="n">
@@ -16682,6 +17595,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q303" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="304">
       <c r="B304" s="0" t="n">
@@ -16733,6 +17649,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q304" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="305">
       <c r="B305" s="0" t="n">
@@ -16784,6 +17703,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q305" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="306">
       <c r="B306" s="0" t="n">
@@ -16835,6 +17757,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=4</t>
         </is>
       </c>
+      <c r="Q306" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="307">
       <c r="B307" s="0" t="n">
@@ -16886,6 +17811,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q307" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="308">
       <c r="B308" s="0" t="n">
@@ -16937,6 +17865,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q308" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="309">
       <c r="B309" s="0" t="n">
@@ -16988,6 +17919,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q309" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="n">
@@ -17039,6 +17973,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q310" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="n">
@@ -17090,6 +18027,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=5</t>
         </is>
       </c>
+      <c r="Q311" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="n">
@@ -17141,6 +18081,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q312" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="313">
       <c r="B313" s="0" t="n">
@@ -17192,6 +18135,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=6</t>
         </is>
       </c>
+      <c r="Q313" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="314">
       <c r="B314" s="0" t="n">
@@ -17243,6 +18189,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q314" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="315">
       <c r="B315" s="0" t="n">
@@ -17294,6 +18243,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=7</t>
         </is>
       </c>
+      <c r="Q315" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="316">
       <c r="B316" s="0" t="n">
@@ -17345,6 +18297,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q316" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="317">
       <c r="B317" s="0" t="n">
@@ -17396,6 +18351,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=8</t>
         </is>
       </c>
+      <c r="Q317" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="318">
       <c r="B318" s="0" t="n">
@@ -17447,6 +18405,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q318" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="319">
       <c r="B319" s="0" t="n">
@@ -17498,6 +18459,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=9</t>
         </is>
       </c>
+      <c r="Q319" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="320">
       <c r="B320" s="0" t="n">
@@ -17549,6 +18513,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q320" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="321">
       <c r="B321" s="0" t="n">
@@ -17600,6 +18567,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=10</t>
         </is>
       </c>
+      <c r="Q321" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="322">
       <c r="B322" s="0" t="n">
@@ -17651,6 +18621,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q322" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="323">
       <c r="B323" s="0" t="n">
@@ -17702,6 +18675,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q323" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="324">
       <c r="B324" s="0" t="n">
@@ -17753,6 +18729,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q324" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="325">
       <c r="B325" s="0" t="n">
@@ -17804,6 +18783,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q325" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="326">
       <c r="B326" s="0" t="n">
@@ -17855,6 +18837,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=11</t>
         </is>
       </c>
+      <c r="Q326" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="327">
       <c r="B327" s="0" t="n">
@@ -17906,6 +18891,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q327" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="328">
       <c r="B328" s="0" t="n">
@@ -17957,6 +18945,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=12</t>
         </is>
       </c>
+      <c r="Q328" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="329">
       <c r="B329" s="0" t="n">
@@ -18008,6 +18999,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q329" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="330">
       <c r="B330" s="0" t="n">
@@ -18059,6 +19053,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=13</t>
         </is>
       </c>
+      <c r="Q330" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="331">
       <c r="B331" s="0" t="n">
@@ -18110,6 +19107,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q331" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="332">
       <c r="B332" s="0" t="n">
@@ -18161,6 +19161,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=14</t>
         </is>
       </c>
+      <c r="Q332" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="333">
       <c r="B333" s="0" t="n">
@@ -18212,6 +19215,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q333" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="334">
       <c r="B334" s="0" t="n">
@@ -18263,6 +19269,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=15</t>
         </is>
       </c>
+      <c r="Q334" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="335">
       <c r="B335" s="0" t="n">
@@ -18314,6 +19323,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q335" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="336">
       <c r="B336" s="0" t="n">
@@ -18365,6 +19377,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q336" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="337">
       <c r="B337" s="0" t="n">
@@ -18416,6 +19431,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q337" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="338">
       <c r="B338" s="0" t="n">
@@ -18467,6 +19485,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q338" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="339">
       <c r="B339" s="0" t="n">
@@ -18518,6 +19539,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=5; wave=16</t>
         </is>
       </c>
+      <c r="Q339" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="340">
       <c r="B340" s="0" t="n">
@@ -18569,6 +19593,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q340" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="341">
       <c r="B341" s="0" t="n">
@@ -18620,6 +19647,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=17</t>
         </is>
       </c>
+      <c r="Q341" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="342">
       <c r="B342" s="0" t="n">
@@ -18671,6 +19701,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q342" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="343">
       <c r="B343" s="0" t="n">
@@ -18722,6 +19755,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=18</t>
         </is>
       </c>
+      <c r="Q343" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="344">
       <c r="B344" s="0" t="n">
@@ -18773,6 +19809,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q344" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="345">
       <c r="B345" s="0" t="n">
@@ -18824,6 +19863,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=19</t>
         </is>
       </c>
+      <c r="Q345" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="346">
       <c r="B346" s="0" t="n">
@@ -18875,6 +19917,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q346" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="347">
       <c r="B347" s="0" t="n">
@@ -18926,6 +19971,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=20</t>
         </is>
       </c>
+      <c r="Q347" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="348">
       <c r="B348" s="0" t="n">
@@ -18977,6 +20025,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q348" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="349">
       <c r="B349" s="0" t="n">
@@ -19028,6 +20079,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=21</t>
         </is>
       </c>
+      <c r="Q349" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="350">
       <c r="B350" s="0" t="n">
@@ -19079,6 +20133,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q350" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="351">
       <c r="B351" s="0" t="n">
@@ -19130,6 +20187,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=22</t>
         </is>
       </c>
+      <c r="Q351" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="352">
       <c r="B352" s="0" t="n">
@@ -19181,6 +20241,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q352" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="353">
       <c r="B353" s="0" t="n">
@@ -19232,6 +20295,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=23</t>
         </is>
       </c>
+      <c r="Q353" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="354">
       <c r="B354" s="0" t="n">
@@ -19283,6 +20349,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q354" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="355">
       <c r="B355" s="0" t="n">
@@ -19334,6 +20403,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=24</t>
         </is>
       </c>
+      <c r="Q355" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="356">
       <c r="B356" s="0" t="n">
@@ -19385,6 +20457,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=5; wave=25</t>
         </is>
       </c>
+      <c r="Q356" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="357">
       <c r="B357" s="0" t="n">
@@ -19435,6 +20510,9 @@
         <is>
           <t>Balance variant; canonical=12; role=air; profile=D04; level=5; wave=25</t>
         </is>
+      </c>
+      <c r="Q357" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
